--- a/plugins/jsh_airport/config/jsh_airport/warehouse-lvl0.xlsx
+++ b/plugins/jsh_airport/config/jsh_airport/warehouse-lvl0.xlsx
@@ -28,199 +28,244 @@
     <t>A-10A</t>
   </si>
   <si>
+    <t>weapons.adapters.lau-88</t>
+  </si>
+  <si>
     <t>A-10C</t>
   </si>
   <si>
+    <t>weapons.bombs.250-2</t>
+  </si>
+  <si>
     <t>A-10C_2</t>
   </si>
   <si>
+    <t>weapons.bombs.250-3</t>
+  </si>
+  <si>
+    <t>weapons.bombs.AB_250_2_SD_10A</t>
+  </si>
+  <si>
     <t>A-20G</t>
   </si>
   <si>
+    <t>weapons.bombs.AB_250_2_SD_2</t>
+  </si>
+  <si>
     <t>A-50</t>
   </si>
   <si>
-    <t>weapons.adapters.lau-88</t>
+    <t>weapons.bombs.AB_500_1_SD_10A</t>
+  </si>
+  <si>
+    <t>A6E</t>
+  </si>
+  <si>
+    <t>weapons.bombs.AGM_62</t>
+  </si>
+  <si>
+    <t>AH-1W</t>
+  </si>
+  <si>
+    <t>weapons.bombs.AGM_62_I</t>
+  </si>
+  <si>
+    <t>AH-64A</t>
+  </si>
+  <si>
+    <t>weapons.bombs.AN_M30A1</t>
+  </si>
+  <si>
+    <t>AH-64D</t>
+  </si>
+  <si>
+    <t>weapons.bombs.AN_M57</t>
+  </si>
+  <si>
+    <t>AH-64D_BLK_II</t>
+  </si>
+  <si>
+    <t>weapons.bombs.AN_M64</t>
+  </si>
+  <si>
+    <t>AJS37</t>
+  </si>
+  <si>
+    <t>weapons.bombs.AN_M65</t>
+  </si>
+  <si>
+    <t>AV8BNA</t>
+  </si>
+  <si>
+    <t>weapons.bombs.AN_M66</t>
+  </si>
+  <si>
+    <t>An-26B</t>
+  </si>
+  <si>
+    <t>weapons.bombs.AO_25SL</t>
+  </si>
+  <si>
+    <t>An-30M</t>
+  </si>
+  <si>
+    <t>weapons.bombs.BAP-100</t>
+  </si>
+  <si>
+    <t>weapons.bombs.BAP_100</t>
+  </si>
+  <si>
+    <t>B-1B</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>A6E</t>
+    <t>B-52H</t>
+  </si>
+  <si>
+    <t>weapons.bombs.BAT-120</t>
+  </si>
+  <si>
+    <t>weapons.bombs.BDU_33</t>
+  </si>
+  <si>
+    <t>Bf-109K-4</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>weapons.bombs.250-2</t>
-  </si>
-  <si>
-    <t>AH-1W</t>
+    <t>weapons.bombs.BDU_45</t>
+  </si>
+  <si>
+    <t>C-101CC</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>weapons.bombs.250-3</t>
-  </si>
-  <si>
-    <t>weapons.bombs.AB_250_2_SD_10A</t>
+    <t>weapons.bombs.BDU_45B</t>
+  </si>
+  <si>
+    <t>C-101EB</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>AH-64A</t>
-  </si>
-  <si>
-    <t>weapons.bombs.AB_250_2_SD_2</t>
-  </si>
-  <si>
-    <t>weapons.bombs.AB_500_1_SD_10A</t>
-  </si>
-  <si>
-    <t>AH-64D</t>
-  </si>
-  <si>
-    <t>weapons.bombs.AGM_62</t>
-  </si>
-  <si>
-    <t>weapons.bombs.AGM_62_I</t>
-  </si>
-  <si>
-    <t>weapons.bombs.AN_M30A1</t>
-  </si>
-  <si>
-    <t>AH-64D_BLK_II</t>
-  </si>
-  <si>
-    <t>weapons.bombs.AN_M57</t>
-  </si>
-  <si>
-    <t>weapons.bombs.AN_M64</t>
-  </si>
-  <si>
-    <t>weapons.bombs.AN_M65</t>
-  </si>
-  <si>
-    <t>AJS37</t>
-  </si>
-  <si>
-    <t>weapons.bombs.AN_M66</t>
-  </si>
-  <si>
-    <t>weapons.bombs.AO_25SL</t>
-  </si>
-  <si>
-    <t>weapons.bombs.BAP-100</t>
-  </si>
-  <si>
-    <t>AV8BNA</t>
-  </si>
-  <si>
-    <t>weapons.bombs.BAP_100</t>
-  </si>
-  <si>
-    <t>An-26B</t>
-  </si>
-  <si>
-    <t>weapons.bombs.BAT-120</t>
-  </si>
-  <si>
-    <t>weapons.bombs.BDU_33</t>
-  </si>
-  <si>
-    <t>weapons.bombs.BDU_45</t>
-  </si>
-  <si>
-    <t>An-30M</t>
-  </si>
-  <si>
-    <t>weapons.bombs.BDU_45B</t>
-  </si>
-  <si>
     <t>weapons.bombs.BDU_45LGB</t>
   </si>
   <si>
-    <t>B-1B</t>
+    <t>C-130</t>
   </si>
   <si>
     <t>weapons.bombs.BDU_50HD</t>
   </si>
   <si>
+    <t>C-130J-30</t>
+  </si>
+  <si>
+    <t>C-17A</t>
+  </si>
+  <si>
+    <t>CH-47D</t>
+  </si>
+  <si>
+    <t>CH-47Fbl1</t>
+  </si>
+  <si>
     <t>weapons.bombs.BDU_50LD</t>
   </si>
   <si>
-    <t>B-52H</t>
-  </si>
-  <si>
     <t>weapons.bombs.BDU_50LGB</t>
   </si>
   <si>
+    <t>CH-53E</t>
+  </si>
+  <si>
     <t>weapons.bombs.BEER_BOMB</t>
   </si>
   <si>
-    <t>Bf-109K-4</t>
+    <t>CHAP_TigerUHT</t>
   </si>
   <si>
     <t>weapons.bombs.BETAB-500M</t>
   </si>
   <si>
+    <t>Christen Eagle II</t>
+  </si>
+  <si>
     <t>weapons.bombs.BETAB-500S</t>
   </si>
   <si>
-    <t>C-101CC</t>
+    <t>E-2C</t>
   </si>
   <si>
     <t>weapons.bombs.BIN_200</t>
   </si>
   <si>
+    <t>E-3A</t>
+  </si>
+  <si>
     <t>weapons.bombs.BKF_AO2_5RT</t>
   </si>
   <si>
     <t>weapons.bombs.BKF_PTAB2_5KO</t>
   </si>
   <si>
-    <t>C-101EB</t>
+    <t>F-100D</t>
   </si>
   <si>
     <t>weapons.bombs.BLG66</t>
   </si>
   <si>
+    <t>F-117A</t>
+  </si>
+  <si>
     <t>weapons.bombs.BLG66_BELOUGA</t>
   </si>
   <si>
+    <t>F-14A</t>
+  </si>
+  <si>
     <t>weapons.bombs.BLG66_EG</t>
   </si>
   <si>
-    <t>C-130</t>
-  </si>
-  <si>
     <t>weapons.bombs.BLU-18/B_GROUP</t>
   </si>
   <si>
+    <t>F-14A-135-GR</t>
+  </si>
+  <si>
     <t>weapons.bombs.BLU-3B_GROUP</t>
   </si>
   <si>
+    <t>F-14A-135-GR-Early</t>
+  </si>
+  <si>
     <t>weapons.bombs.BLU-3B_R_GROUP_R</t>
   </si>
   <si>
+    <t>F-14A-95-GR</t>
+  </si>
+  <si>
     <t>weapons.bombs.BLU-3_GROUP</t>
   </si>
   <si>
-    <t>C-130J-30</t>
-  </si>
-  <si>
     <t>weapons.bombs.BLU-3_R_GROUP_R</t>
   </si>
   <si>
+    <t>F-14B</t>
+  </si>
+  <si>
     <t>weapons.bombs.BLU-49/B</t>
   </si>
   <si>
     <t>weapons.bombs.BLU-4B_GROUP</t>
   </si>
   <si>
-    <t>C-17A</t>
+    <t>F-14BU</t>
   </si>
   <si>
     <t>weapons.bombs.BLU-4B_R_GROUP_R</t>
@@ -232,9 +277,6 @@
     <t>weapons.bombs.BOLT-117</t>
   </si>
   <si>
-    <t>CH-47D</t>
-  </si>
-  <si>
     <t>weapons.bombs.BR_250</t>
   </si>
   <si>
@@ -244,67 +286,85 @@
     <t>weapons.bombs.BetAB_500</t>
   </si>
   <si>
-    <t>CH-47Fbl1</t>
-  </si>
-  <si>
     <t>weapons.bombs.BetAB_500ShP</t>
   </si>
   <si>
     <t>weapons.bombs.British_GP_250LB_Bomb_Mk1</t>
   </si>
   <si>
+    <t>F-15C</t>
+  </si>
+  <si>
     <t>weapons.bombs.British_GP_250LB_Bomb_Mk4</t>
   </si>
   <si>
-    <t>CH-53E</t>
+    <t>F-15E</t>
   </si>
   <si>
     <t>weapons.bombs.British_GP_250LB_Bomb_Mk5</t>
   </si>
   <si>
+    <t>F-15ESE</t>
+  </si>
+  <si>
     <t>weapons.bombs.British_GP_500LB_Bomb_Mk1</t>
   </si>
   <si>
+    <t>F-16A</t>
+  </si>
+  <si>
     <t>weapons.bombs.British_GP_500LB_Bomb_Mk4</t>
   </si>
   <si>
-    <t>CHAP_TigerUHT</t>
+    <t>F-16C bl.50</t>
   </si>
   <si>
     <t>weapons.bombs.British_GP_500LB_Bomb_Mk4_Short</t>
   </si>
   <si>
+    <t>F-16C_50</t>
+  </si>
+  <si>
     <t>weapons.bombs.British_GP_500LB_Bomb_Mk5</t>
   </si>
   <si>
     <t>weapons.bombs.British_MC_250LB_Bomb_Mk1</t>
   </si>
   <si>
-    <t>Christen Eagle II</t>
+    <t>F-4E</t>
   </si>
   <si>
     <t>weapons.bombs.British_MC_250LB_Bomb_Mk2</t>
   </si>
   <si>
+    <t>F-4E-45MC</t>
+  </si>
+  <si>
     <t>weapons.bombs.British_MC_500LB_Bomb_Mk1_Short</t>
   </si>
   <si>
     <t>weapons.bombs.British_MC_500LB_Bomb_Mk2</t>
   </si>
   <si>
-    <t>E-2C</t>
+    <t>F-5E</t>
   </si>
   <si>
     <t>weapons.bombs.British_SAP_250LB_Bomb_Mk5</t>
   </si>
   <si>
+    <t>F-5E-3</t>
+  </si>
+  <si>
     <t>weapons.bombs.British_SAP_500LB_Bomb_Mk5</t>
   </si>
   <si>
+    <t>F-5E-3_FC</t>
+  </si>
+  <si>
     <t>weapons.bombs.CBU_103</t>
   </si>
   <si>
-    <t>E-3A</t>
+    <t>F-86F Sabre</t>
   </si>
   <si>
     <t>weapons.bombs.CBU_105</t>
@@ -313,28 +373,34 @@
     <t>weapons.bombs.CBU_52B</t>
   </si>
   <si>
-    <t>F-100D</t>
+    <t>F-86F_FC</t>
   </si>
   <si>
     <t>weapons.bombs.CBU_87</t>
   </si>
   <si>
+    <t>F/A-18A</t>
+  </si>
+  <si>
     <t>weapons.bombs.CBU_97</t>
   </si>
   <si>
+    <t>F/A-18C</t>
+  </si>
+  <si>
     <t>weapons.bombs.CBU_99</t>
   </si>
   <si>
-    <t>F-117A</t>
-  </si>
-  <si>
     <t>weapons.bombs.Durandal</t>
   </si>
   <si>
+    <t>F4U-1D</t>
+  </si>
+  <si>
     <t>weapons.bombs.FAB-250-M62</t>
   </si>
   <si>
-    <t>F-14A</t>
+    <t>F4U-1D_CW</t>
   </si>
   <si>
     <t>weapons.bombs.FAB-250M54</t>
@@ -343,28 +409,37 @@
     <t>weapons.bombs.FAB-250M54TU</t>
   </si>
   <si>
+    <t>FA-18C_hornet</t>
+  </si>
+  <si>
     <t>weapons.bombs.FAB-500M54</t>
   </si>
   <si>
+    <t>FW-190A8</t>
+  </si>
+  <si>
     <t>weapons.bombs.FAB-500M54TU</t>
   </si>
   <si>
-    <t>F-14A-135-GR</t>
-  </si>
-  <si>
     <t>weapons.bombs.FAB-500SL</t>
   </si>
   <si>
+    <t>FW-190D9</t>
+  </si>
+  <si>
     <t>weapons.bombs.FAB-500TA</t>
   </si>
   <si>
     <t>weapons.bombs.FAB_100</t>
   </si>
   <si>
+    <t>Falcon_Gyrocopter</t>
+  </si>
+  <si>
     <t>weapons.bombs.FAB_100M</t>
   </si>
   <si>
-    <t>F-14A-135-GR-Early</t>
+    <t>H-6J</t>
   </si>
   <si>
     <t>weapons.bombs.FAB_100SV</t>
@@ -373,31 +448,40 @@
     <t>weapons.bombs.FAB_1500</t>
   </si>
   <si>
+    <t>Hawk</t>
+  </si>
+  <si>
     <t>weapons.bombs.FAB_250</t>
   </si>
   <si>
-    <t>F-14A-95-GR</t>
-  </si>
-  <si>
     <t>weapons.bombs.FAB_50</t>
   </si>
   <si>
+    <t>I-16</t>
+  </si>
+  <si>
     <t>weapons.bombs.FAB_500</t>
   </si>
   <si>
-    <t>F-14B</t>
+    <t>IL-76MD</t>
   </si>
   <si>
     <t>weapons.bombs.GBU_10</t>
   </si>
   <si>
+    <t>IL-78M</t>
+  </si>
+  <si>
     <t>weapons.bombs.GBU_12</t>
   </si>
   <si>
+    <t>J-11A</t>
+  </si>
+  <si>
     <t>weapons.bombs.GBU_15_V_1_B</t>
   </si>
   <si>
-    <t>F-14BU</t>
+    <t>JF-17</t>
   </si>
   <si>
     <t>weapons.bombs.GBU_15_V_31_B</t>
@@ -406,124 +490,175 @@
     <t>weapons.bombs.GBU_16</t>
   </si>
   <si>
+    <t>KC-135</t>
+  </si>
+  <si>
     <t>weapons.bombs.GBU_24</t>
   </si>
   <si>
+    <t>KC130</t>
+  </si>
+  <si>
     <t>weapons.bombs.GBU_27</t>
   </si>
   <si>
+    <t>KC135MPRS</t>
+  </si>
+  <si>
     <t>weapons.bombs.GBU_28</t>
   </si>
   <si>
     <t>weapons.bombs.GBU_31</t>
   </si>
   <si>
+    <t>KJ-2000</t>
+  </si>
+  <si>
     <t>weapons.bombs.GBU_31_V_2B</t>
   </si>
   <si>
+    <t>Ka-27</t>
+  </si>
+  <si>
     <t>weapons.bombs.GBU_31_V_3B</t>
   </si>
   <si>
+    <t>Ka-50</t>
+  </si>
+  <si>
     <t>weapons.bombs.GBU_31_V_4B</t>
   </si>
   <si>
+    <t>Ka-50_3</t>
+  </si>
+  <si>
     <t>weapons.bombs.GBU_32_V_2B</t>
   </si>
   <si>
+    <t>L-39C</t>
+  </si>
+  <si>
     <t>weapons.bombs.GBU_38</t>
   </si>
   <si>
+    <t>L-39ZA</t>
+  </si>
+  <si>
     <t>weapons.bombs.GBU_39</t>
   </si>
   <si>
     <t>weapons.bombs.GBU_43</t>
   </si>
   <si>
+    <t>La-7</t>
+  </si>
+  <si>
     <t>weapons.bombs.GBU_54_V_1B</t>
   </si>
   <si>
+    <t>M-2000C</t>
+  </si>
+  <si>
     <t>weapons.bombs.GBU_8_B</t>
   </si>
   <si>
+    <t>MB-339A</t>
+  </si>
+  <si>
     <t>weapons.bombs.HB_F4E_GBU15V1</t>
   </si>
   <si>
+    <t>MB-339APAN</t>
+  </si>
+  <si>
     <t>weapons.bombs.HEBOMB</t>
   </si>
   <si>
+    <t>MQ-9 Reaper</t>
+  </si>
+  <si>
     <t>weapons.bombs.HEBOMBD</t>
   </si>
   <si>
     <t>weapons.bombs.IAB-500</t>
   </si>
   <si>
-    <t>F-15C</t>
+    <t>Mi-24P</t>
   </si>
   <si>
     <t>weapons.bombs.KAB_1500Kr</t>
   </si>
   <si>
+    <t>Mi-24V</t>
+  </si>
+  <si>
     <t>weapons.bombs.KAB_1500LG</t>
   </si>
   <si>
+    <t>Mi-26</t>
+  </si>
+  <si>
     <t>weapons.bombs.KAB_1500T</t>
   </si>
   <si>
-    <t>F-15E</t>
-  </si>
-  <si>
     <t>weapons.bombs.KAB_500</t>
   </si>
   <si>
     <t>weapons.bombs.KAB_500Kr</t>
   </si>
   <si>
+    <t>Mi-28N</t>
+  </si>
+  <si>
     <t>weapons.bombs.KAB_500S</t>
   </si>
   <si>
-    <t>F-15ESE</t>
-  </si>
-  <si>
     <t>weapons.bombs.LS_6_100</t>
   </si>
   <si>
+    <t>Mi-8MT</t>
+  </si>
+  <si>
     <t>weapons.bombs.LUU_2B</t>
   </si>
   <si>
-    <t>F-16A</t>
-  </si>
-  <si>
     <t>weapons.bombs.LYSBOMB 11086</t>
   </si>
   <si>
+    <t>MiG-15bis</t>
+  </si>
+  <si>
     <t>weapons.bombs.LYSBOMB 11087</t>
   </si>
   <si>
-    <t>F-16C bl.50</t>
-  </si>
-  <si>
-    <t>F-16C_50</t>
+    <t>MiG-15bis_FC</t>
   </si>
   <si>
     <t>weapons.bombs.LYSBOMB 11088</t>
   </si>
   <si>
+    <t>MiG-19P</t>
+  </si>
+  <si>
     <t>weapons.bombs.LYSBOMB 11089</t>
   </si>
   <si>
-    <t>F-4E</t>
-  </si>
-  <si>
     <t>weapons.bombs.MK106</t>
   </si>
   <si>
+    <t>MiG-21Bis</t>
+  </si>
+  <si>
     <t>weapons.bombs.MK76</t>
   </si>
   <si>
+    <t>MiG-23MLD</t>
+  </si>
+  <si>
     <t>weapons.bombs.MK_82AIR</t>
   </si>
   <si>
-    <t>F-4E-45MC</t>
+    <t>MiG-25PD</t>
   </si>
   <si>
     <t>weapons.bombs.MK_82SNAKEYE</t>
@@ -532,46 +667,52 @@
     <t>weapons.bombs.M_117</t>
   </si>
   <si>
-    <t>F-5E</t>
+    <t>MiG-25RBT</t>
   </si>
   <si>
     <t>weapons.bombs.Mk_81</t>
   </si>
   <si>
+    <t>MiG-27K</t>
+  </si>
+  <si>
     <t>weapons.bombs.Mk_82</t>
   </si>
   <si>
-    <t>F-5E-3</t>
+    <t>MiG-29 Fulcrum</t>
   </si>
   <si>
     <t>weapons.bombs.Mk_82Y</t>
   </si>
   <si>
+    <t>MiG-29A</t>
+  </si>
+  <si>
     <t>weapons.bombs.Mk_83</t>
   </si>
   <si>
-    <t>F-5E-3_FC</t>
-  </si>
-  <si>
     <t>weapons.bombs.Mk_83AIR</t>
   </si>
   <si>
+    <t>MiG-29G</t>
+  </si>
+  <si>
     <t>weapons.bombs.Mk_83CT</t>
   </si>
   <si>
     <t>weapons.bombs.Mk_84</t>
   </si>
   <si>
-    <t>F-86F Sabre</t>
-  </si>
-  <si>
     <t>weapons.bombs.Mk_84AIR_GP</t>
   </si>
   <si>
+    <t>MiG-29S</t>
+  </si>
+  <si>
     <t>weapons.bombs.Mk_84AIR_TP</t>
   </si>
   <si>
-    <t>F-86F_FC</t>
+    <t>MiG-31</t>
   </si>
   <si>
     <t>weapons.bombs.ODAB-500PM</t>
@@ -580,28 +721,28 @@
     <t>weapons.bombs.OFAB-100 Jupiter</t>
   </si>
   <si>
+    <t>Mirage 2000-5</t>
+  </si>
+  <si>
     <t>weapons.bombs.OFAB-100-120TU</t>
   </si>
   <si>
-    <t>F/A-18A</t>
+    <t>Mirage-F1AD</t>
   </si>
   <si>
     <t>weapons.bombs.OH58D_Blue_Smoke_Grenade</t>
   </si>
   <si>
-    <t>F/A-18C</t>
+    <t>Mirage-F1AZ</t>
   </si>
   <si>
     <t>weapons.bombs.OH58D_Green_Smoke_Grenade</t>
   </si>
   <si>
-    <t>F4U-1D</t>
-  </si>
-  <si>
     <t>weapons.bombs.OH58D_Red_Smoke_Grenade</t>
   </si>
   <si>
-    <t>F4U-1D_CW</t>
+    <t>Mirage-F1B</t>
   </si>
   <si>
     <t>weapons.bombs.OH58D_Violet_Smoke_Grenade</t>
@@ -610,7 +751,7 @@
     <t>weapons.bombs.OH58D_White_Smoke_Grenade</t>
   </si>
   <si>
-    <t>FA-18C_hornet</t>
+    <t>Mirage-F1BD</t>
   </si>
   <si>
     <t>weapons.bombs.OH58D_Yellow_Smoke_Grenade</t>
@@ -619,7 +760,7 @@
     <t>weapons.bombs.P-50T</t>
   </si>
   <si>
-    <t>FW-190A8</t>
+    <t>Mirage-F1BE</t>
   </si>
   <si>
     <t>weapons.bombs.RBK_250</t>
@@ -628,7 +769,7 @@
     <t>weapons.bombs.RBK_250_275_AO_1SCH</t>
   </si>
   <si>
-    <t>FW-190D9</t>
+    <t>Mirage-F1BQ</t>
   </si>
   <si>
     <t>weapons.bombs.RBK_500AO</t>
@@ -637,25 +778,22 @@
     <t>weapons.bombs.RBK_500U</t>
   </si>
   <si>
-    <t>Falcon_Gyrocopter</t>
+    <t>Mirage-F1C</t>
   </si>
   <si>
     <t>weapons.bombs.RBK_500U_OAB_2_5RT</t>
   </si>
   <si>
-    <t>H-6J</t>
+    <t>Mirage-F1C-200</t>
   </si>
   <si>
     <t>weapons.bombs.ROCKEYE</t>
   </si>
   <si>
-    <t>Hawk</t>
-  </si>
-  <si>
     <t>weapons.bombs.SAB_100MN</t>
   </si>
   <si>
-    <t>I-16</t>
+    <t>Mirage-F1CE</t>
   </si>
   <si>
     <t>weapons.bombs.SAB_250_200</t>
@@ -664,7 +802,7 @@
     <t>weapons.bombs.SAMP125LD</t>
   </si>
   <si>
-    <t>IL-76MD</t>
+    <t>Mirage-F1CG</t>
   </si>
   <si>
     <t>weapons.bombs.SAMP250HD</t>
@@ -673,67 +811,70 @@
     <t>weapons.bombs.SAMP250LD</t>
   </si>
   <si>
-    <t>IL-78M</t>
+    <t>Mirage-F1CH</t>
   </si>
   <si>
     <t>weapons.bombs.SAMP400HD</t>
   </si>
   <si>
+    <t>Mirage-F1CJ</t>
+  </si>
+  <si>
     <t>weapons.bombs.SAMP400LD</t>
   </si>
   <si>
-    <t>J-11A</t>
-  </si>
-  <si>
     <t>weapons.bombs.SC_250_T1_L2</t>
   </si>
   <si>
+    <t>Mirage-F1CK</t>
+  </si>
+  <si>
     <t>weapons.bombs.SC_250_T3_J</t>
   </si>
   <si>
-    <t>JF-17</t>
-  </si>
-  <si>
     <t>weapons.bombs.SC_50</t>
   </si>
   <si>
+    <t>Mirage-F1CR</t>
+  </si>
+  <si>
     <t>weapons.bombs.SC_500_J</t>
   </si>
   <si>
-    <t>KC-135</t>
+    <t>Mirage-F1CT</t>
   </si>
   <si>
     <t>weapons.bombs.SC_500_L2</t>
   </si>
   <si>
-    <t>KC130</t>
-  </si>
-  <si>
     <t>weapons.bombs.SD_250_Stg</t>
   </si>
   <si>
+    <t>Mirage-F1CZ</t>
+  </si>
+  <si>
     <t>weapons.bombs.SD_500_A</t>
   </si>
   <si>
-    <t>KC135MPRS</t>
-  </si>
-  <si>
     <t>weapons.bombs.Type_200A</t>
   </si>
   <si>
+    <t>Mirage-F1DDA</t>
+  </si>
+  <si>
     <t>weapons.containers.16c_hts_pod</t>
   </si>
   <si>
-    <t>KJ-2000</t>
-  </si>
-  <si>
     <t>weapons.containers.AAQ-28_LITENING</t>
   </si>
   <si>
+    <t>Mirage-F1ED</t>
+  </si>
+  <si>
     <t>weapons.containers.AIM-9S</t>
   </si>
   <si>
-    <t>Ka-27</t>
+    <t>Mirage-F1EDA</t>
   </si>
   <si>
     <t>weapons.containers.ALQ-131</t>
@@ -742,7 +883,7 @@
     <t>weapons.containers.ALQ-184</t>
   </si>
   <si>
-    <t>Ka-50</t>
+    <t>Mirage-F1EE</t>
   </si>
   <si>
     <t>weapons.containers.ANAWW_13</t>
@@ -751,112 +892,154 @@
     <t>weapons.containers.AN_AAQ_33</t>
   </si>
   <si>
-    <t>Ka-50_3</t>
+    <t>Mirage-F1EH</t>
   </si>
   <si>
     <t>weapons.containers.AN_ASQ_228</t>
   </si>
   <si>
+    <t>Mirage-F1EQ</t>
+  </si>
+  <si>
     <t>weapons.containers.APK-9</t>
   </si>
   <si>
-    <t>L-39C</t>
-  </si>
-  <si>
     <t>weapons.containers.ASO-2</t>
   </si>
   <si>
+    <t>Mirage-F1JA</t>
+  </si>
+  <si>
     <t>weapons.containers.AV8BNA_ALQ164</t>
   </si>
   <si>
-    <t>L-39ZA</t>
-  </si>
-  <si>
     <t>weapons.containers.BARAX</t>
   </si>
   <si>
+    <t>Mirage-F1M-CE</t>
+  </si>
+  <si>
     <t>weapons.containers.BOZ-100</t>
   </si>
   <si>
     <t>weapons.containers.BRD-4-250</t>
   </si>
   <si>
+    <t>Mirage-F1M-EE</t>
+  </si>
+  <si>
     <t>weapons.containers.ETHER</t>
   </si>
   <si>
+    <t>MosquitoFBMkVI</t>
+  </si>
+  <si>
     <t>weapons.containers.F-15E_AAQ-13_LANTIRN</t>
   </si>
   <si>
     <t>weapons.containers.F-15E_AAQ-14_LANTIRN</t>
   </si>
   <si>
+    <t>OH-58D</t>
+  </si>
+  <si>
     <t>weapons.containers.F-15E_AAQ-28_LITENING</t>
   </si>
   <si>
     <t>weapons.containers.F-15E_AAQ-33_XR_ATP-SE</t>
   </si>
   <si>
+    <t>OH58D</t>
+  </si>
+  <si>
     <t>weapons.containers.F-15E_AXQ-14_DATALINK</t>
   </si>
   <si>
+    <t>P-47D-30</t>
+  </si>
+  <si>
     <t>weapons.containers.F-18-FLIR-POD</t>
   </si>
   <si>
     <t>weapons.containers.F-18-LDT-POD</t>
   </si>
   <si>
+    <t>P-47D-30bl1</t>
+  </si>
+  <si>
     <t>weapons.containers.F100_CAMERA_KA71A</t>
   </si>
   <si>
+    <t>P-47D-40</t>
+  </si>
+  <si>
     <t>weapons.containers.F100_CAMERA_P2</t>
   </si>
   <si>
     <t>weapons.containers.FAS</t>
   </si>
   <si>
+    <t>P-51D</t>
+  </si>
+  <si>
     <t>weapons.containers.Fantasm</t>
   </si>
   <si>
-    <t>La-7</t>
+    <t>P-51D-30-NA</t>
   </si>
   <si>
     <t>weapons.containers.GD_F100_STRIKE_CAMERA</t>
   </si>
   <si>
+    <t>QF-4E</t>
+  </si>
+  <si>
     <t>weapons.containers.GUV_VOG</t>
   </si>
   <si>
-    <t>M-2000C</t>
+    <t>RQ-1A Predator</t>
   </si>
   <si>
     <t>weapons.containers.GUV_YakB_GSHP</t>
   </si>
   <si>
+    <t>S-3B</t>
+  </si>
+  <si>
     <t>weapons.containers.HB_ALE_40_0_0</t>
   </si>
   <si>
+    <t>S-3B Tanker</t>
+  </si>
+  <si>
     <t>weapons.containers.HB_ALE_40_0_120</t>
   </si>
   <si>
-    <t>MB-339A</t>
+    <t>SA342L</t>
   </si>
   <si>
     <t>weapons.containers.HB_ALE_40_15_90</t>
   </si>
   <si>
+    <t>SA342M</t>
+  </si>
+  <si>
     <t>weapons.containers.HB_ALE_40_30_0</t>
   </si>
   <si>
-    <t>MB-339APAN</t>
+    <t>SA342Minigun</t>
   </si>
   <si>
     <t>weapons.containers.HB_ALE_40_30_60</t>
   </si>
   <si>
+    <t>SA342Mistral</t>
+  </si>
+  <si>
     <t>weapons.containers.HB_F14_EXT_AN_APQ-167</t>
   </si>
   <si>
-    <t>MQ-9 Reaper</t>
+    <t>SH-3W</t>
   </si>
   <si>
     <t>weapons.containers.HB_F14_EXT_ECA</t>
@@ -865,7 +1048,7 @@
     <t>weapons.containers.HB_F14_EXT_TARPS</t>
   </si>
   <si>
-    <t>Mi-24P</t>
+    <t>SH-60B</t>
   </si>
   <si>
     <t>weapons.containers.HB_ORD_Pave_Spike</t>
@@ -874,40 +1057,52 @@
     <t>weapons.containers.HB_ORD_Pave_Spike_Fast</t>
   </si>
   <si>
+    <t>SpitfireLFMkIX</t>
+  </si>
+  <si>
     <t>weapons.containers.HVAR_rocket</t>
   </si>
   <si>
+    <t>SpitfireLFMkIXCW</t>
+  </si>
+  <si>
     <t>weapons.containers.IRDeflector</t>
   </si>
   <si>
     <t>weapons.containers.KBpod</t>
   </si>
   <si>
+    <t>Su-17M4</t>
+  </si>
+  <si>
     <t>weapons.containers.KINGAL</t>
   </si>
   <si>
+    <t>Su-24M</t>
+  </si>
+  <si>
     <t>weapons.containers.KORD_12_7</t>
   </si>
   <si>
-    <t>Mi-24V</t>
-  </si>
-  <si>
     <t>weapons.containers.KORD_12_7_MI24_L</t>
   </si>
   <si>
+    <t>Su-24MR</t>
+  </si>
+  <si>
     <t>weapons.containers.KORD_12_7_MI24_R</t>
   </si>
   <si>
-    <t>Mi-26</t>
-  </si>
-  <si>
     <t>weapons.containers.LANTIRN</t>
   </si>
   <si>
+    <t>Su-25</t>
+  </si>
+  <si>
     <t>weapons.containers.LANTIRN-F14-TARGET</t>
   </si>
   <si>
-    <t>Mi-28N</t>
+    <t>Su-25T</t>
   </si>
   <si>
     <t>weapons.containers.M134_L</t>
@@ -916,16 +1111,19 @@
     <t>weapons.containers.M134_R</t>
   </si>
   <si>
-    <t>Mi-8MT</t>
+    <t>Su-25TM</t>
   </si>
   <si>
     <t>weapons.containers.M134_SIDE_L</t>
   </si>
   <si>
+    <t>Su-27</t>
+  </si>
+  <si>
     <t>weapons.containers.M134_SIDE_R</t>
   </si>
   <si>
-    <t>MiG-15bis</t>
+    <t>Su-30</t>
   </si>
   <si>
     <t>weapons.containers.M60_SIDE_L</t>
@@ -934,34 +1132,37 @@
     <t>weapons.containers.M60_SIDE_R</t>
   </si>
   <si>
-    <t>MiG-15bis_FC</t>
+    <t>Su-33</t>
   </si>
   <si>
     <t>weapons.containers.MATRA-PHIMAT</t>
   </si>
   <si>
+    <t>Su-34</t>
+  </si>
+  <si>
     <t>weapons.containers.MB339_SMOKE-POD</t>
   </si>
   <si>
-    <t>MiG-19P</t>
-  </si>
-  <si>
     <t>weapons.containers.MB339_TravelPod</t>
   </si>
   <si>
+    <t>TF-51D</t>
+  </si>
+  <si>
     <t>weapons.containers.MB339_Vinten</t>
   </si>
   <si>
-    <t>MiG-21Bis</t>
-  </si>
-  <si>
     <t>weapons.containers.MPS-410</t>
   </si>
   <si>
+    <t>Tornado GR4</t>
+  </si>
+  <si>
     <t>weapons.containers.MXU-648</t>
   </si>
   <si>
-    <t>MiG-23MLD</t>
+    <t>Tornado IDS</t>
   </si>
   <si>
     <t>weapons.containers.OH58D_M3P_L100</t>
@@ -970,19 +1171,22 @@
     <t>weapons.containers.OH58D_M3P_L200</t>
   </si>
   <si>
+    <t>Tu-142</t>
+  </si>
+  <si>
     <t>weapons.containers.OH58D_M3P_L300</t>
   </si>
   <si>
-    <t>MiG-25PD</t>
-  </si>
-  <si>
     <t>weapons.containers.OH58D_M3P_L400</t>
   </si>
   <si>
+    <t>Tu-160</t>
+  </si>
+  <si>
     <t>weapons.containers.OH58D_M3P_L500</t>
   </si>
   <si>
-    <t>MiG-25RBT</t>
+    <t>Tu-22M3</t>
   </si>
   <si>
     <t>weapons.containers.PAVETACK</t>
@@ -991,22 +1195,22 @@
     <t>weapons.containers.PKT_7_62</t>
   </si>
   <si>
-    <t>MiG-27K</t>
+    <t>Tu-95MS</t>
   </si>
   <si>
     <t>weapons.containers.R-73U</t>
   </si>
   <si>
+    <t>UH-1H</t>
+  </si>
+  <si>
     <t>weapons.containers.SHPIL</t>
   </si>
   <si>
-    <t>MiG-29 Fulcrum</t>
-  </si>
-  <si>
     <t>weapons.containers.SKY_SHADOW</t>
   </si>
   <si>
-    <t>MiG-29A</t>
+    <t>UH-60A</t>
   </si>
   <si>
     <t>weapons.containers.SORBCIJA_L</t>
@@ -1015,19 +1219,16 @@
     <t>weapons.containers.SORBCIJA_R</t>
   </si>
   <si>
-    <t>MiG-29G</t>
+    <t>WingLoong-I</t>
   </si>
   <si>
     <t>weapons.containers.SPRD-99</t>
   </si>
   <si>
-    <t>MiG-29S</t>
-  </si>
-  <si>
     <t>weapons.containers.SPS-141</t>
   </si>
   <si>
-    <t>MiG-31</t>
+    <t>Yak-40</t>
   </si>
   <si>
     <t>weapons.containers.SPS-141-100</t>
@@ -1036,7 +1237,7 @@
     <t>weapons.containers.Spear</t>
   </si>
   <si>
-    <t>Mirage 2000-5</t>
+    <t>Yak-52</t>
   </si>
   <si>
     <t>weapons.containers.TANGAZH</t>
@@ -1045,36 +1246,24 @@
     <t>weapons.containers.U22</t>
   </si>
   <si>
-    <t>Mirage-F1AD</t>
-  </si>
-  <si>
     <t>weapons.containers.U22A</t>
   </si>
   <si>
     <t>weapons.containers.aaq-28LEFT litening</t>
   </si>
   <si>
-    <t>Mirage-F1AZ</t>
-  </si>
-  <si>
     <t>weapons.containers.ah-64d_radar</t>
   </si>
   <si>
     <t>weapons.containers.ais-pod-t50_r</t>
   </si>
   <si>
-    <t>Mirage-F1B</t>
-  </si>
-  <si>
     <t>weapons.containers.alq-184long</t>
   </si>
   <si>
     <t>weapons.containers.dlpod_akg</t>
   </si>
   <si>
-    <t>Mirage-F1BD</t>
-  </si>
-  <si>
     <t>weapons.containers.hvar_SmokeGenerator</t>
   </si>
   <si>
@@ -1087,42 +1276,27 @@
     <t>weapons.containers.sa342_dipole_antenna</t>
   </si>
   <si>
-    <t>Mirage-F1BE</t>
-  </si>
-  <si>
     <t>weapons.containers.smoke_pod</t>
   </si>
   <si>
-    <t>Mirage-F1BQ</t>
-  </si>
-  <si>
     <t>weapons.containers.wmd7</t>
   </si>
   <si>
     <t>weapons.containers.{05544F1A-C39C-466b-BC37-5BD1D52E57BB}</t>
   </si>
   <si>
-    <t>Mirage-F1C</t>
-  </si>
-  <si>
     <t>weapons.containers.{ADEN_GUNPOD}</t>
   </si>
   <si>
     <t>weapons.containers.{AKAN_NO_TRC}</t>
   </si>
   <si>
-    <t>Mirage-F1C-200</t>
-  </si>
-  <si>
     <t>weapons.containers.{AKAN}</t>
   </si>
   <si>
     <t>weapons.containers.{AN-M3}</t>
   </si>
   <si>
-    <t>Mirage-F1CE</t>
-  </si>
-  <si>
     <t>weapons.containers.{C-101-DEFA553}</t>
   </si>
   <si>
@@ -1132,156 +1306,99 @@
     <t>weapons.containers.{C130-M18-Sidearm}</t>
   </si>
   <si>
-    <t>Mirage-F1CG</t>
-  </si>
-  <si>
     <t>weapons.containers.{CC420_GUN_POD}</t>
   </si>
   <si>
     <t>weapons.containers.{CE2_SMOKE_WHITE}</t>
   </si>
   <si>
-    <t>Mirage-F1CH</t>
-  </si>
-  <si>
     <t>weapons.containers.{CH47_AFT_M240H}</t>
   </si>
   <si>
     <t>weapons.containers.{CH47_AFT_M3M}</t>
   </si>
   <si>
-    <t>Mirage-F1CJ</t>
-  </si>
-  <si>
     <t>weapons.containers.{CH47_AFT_M60D}</t>
   </si>
   <si>
     <t>weapons.containers.{CH47_PORT_M134D}</t>
   </si>
   <si>
-    <t>Mirage-F1CK</t>
-  </si>
-  <si>
     <t>weapons.containers.{CH47_PORT_M240H}</t>
   </si>
   <si>
     <t>weapons.containers.{CH47_PORT_M60D}</t>
   </si>
   <si>
-    <t>Mirage-F1CR</t>
-  </si>
-  <si>
     <t>weapons.containers.{CH47_STBD_M134D}</t>
   </si>
   <si>
-    <t>Mirage-F1CT</t>
-  </si>
-  <si>
     <t>weapons.containers.{CH47_STBD_M240H}</t>
   </si>
   <si>
-    <t>Mirage-F1CZ</t>
-  </si>
-  <si>
     <t>weapons.containers.{CH47_STBD_M60D}</t>
   </si>
   <si>
     <t>weapons.containers.{CHAP_HMP400LC}</t>
   </si>
   <si>
-    <t>Mirage-F1DDA</t>
-  </si>
-  <si>
     <t>weapons.containers.{E92CBFE5-C153-11d8-9897-000476191836}</t>
   </si>
   <si>
     <t>weapons.containers.{ECM_POD_L_175V}</t>
   </si>
   <si>
-    <t>Mirage-F1ED</t>
-  </si>
-  <si>
     <t>weapons.containers.{EclairM_06}</t>
   </si>
   <si>
     <t>weapons.containers.{EclairM_15}</t>
   </si>
   <si>
-    <t>Mirage-F1EDA</t>
-  </si>
-  <si>
     <t>weapons.containers.{EclairM_24}</t>
   </si>
   <si>
-    <t>Mirage-F1EE</t>
-  </si>
-  <si>
-    <t>Mirage-F1EH</t>
-  </si>
-  <si>
     <t>weapons.containers.{EclairM_33}</t>
   </si>
   <si>
     <t>weapons.containers.{EclairM_42}</t>
   </si>
   <si>
-    <t>Mirage-F1EQ</t>
-  </si>
-  <si>
     <t>weapons.containers.{EclairM_51}</t>
   </si>
   <si>
     <t>weapons.containers.{EclairM_60}</t>
   </si>
   <si>
-    <t>Mirage-F1JA</t>
-  </si>
-  <si>
     <t>weapons.containers.{Eclair}</t>
   </si>
   <si>
     <t>weapons.containers.{F14-LANTIRN-TP}</t>
   </si>
   <si>
-    <t>Mirage-F1M-CE</t>
-  </si>
-  <si>
     <t>weapons.containers.{F4U1D_SMOKE_WHITE}</t>
   </si>
   <si>
     <t>weapons.containers.{FN_HMP400_100}</t>
   </si>
   <si>
-    <t>Mirage-F1M-EE</t>
-  </si>
-  <si>
     <t>weapons.containers.{FN_HMP400_200}</t>
   </si>
   <si>
     <t>weapons.containers.{FN_HMP400}</t>
   </si>
   <si>
-    <t>MosquitoFBMkVI</t>
-  </si>
-  <si>
     <t>weapons.containers.{GAU_12_Equalizer_AP}</t>
   </si>
   <si>
     <t>weapons.containers.{GAU_12_Equalizer_HE}</t>
   </si>
   <si>
-    <t>OH-58D</t>
-  </si>
-  <si>
     <t>weapons.containers.{GAU_12_Equalizer}</t>
   </si>
   <si>
     <t>weapons.containers.{GIAT_M621_APHE}</t>
   </si>
   <si>
-    <t>OH58D</t>
-  </si>
-  <si>
     <t>weapons.containers.{GIAT_M621_AP}</t>
   </si>
   <si>
@@ -1294,105 +1411,66 @@
     <t>weapons.containers.{GIAT_M621_SAPHEI}</t>
   </si>
   <si>
-    <t>P-47D-30</t>
-  </si>
-  <si>
     <t>weapons.containers.{GPU_5_POD}</t>
   </si>
   <si>
-    <t>P-47D-30bl1</t>
-  </si>
-  <si>
     <t>weapons.containers.{INV-SMOKE-BLUE}</t>
   </si>
   <si>
     <t>weapons.containers.{INV-SMOKE-GREEN}</t>
   </si>
   <si>
-    <t>P-47D-40</t>
-  </si>
-  <si>
     <t>weapons.containers.{INV-SMOKE-ORANGE}</t>
   </si>
   <si>
     <t>weapons.containers.{INV-SMOKE-WHITE}</t>
   </si>
   <si>
-    <t>P-51D</t>
-  </si>
-  <si>
     <t>weapons.containers.{INV-SMOKE-YELLOW}</t>
   </si>
   <si>
     <t>weapons.containers.{M2KC_AAF}</t>
   </si>
   <si>
-    <t>P-51D-30-NA</t>
-  </si>
-  <si>
     <t>weapons.containers.{M2KC_AGF}</t>
   </si>
   <si>
     <t>weapons.containers.{MB339_ANM3_L}</t>
   </si>
   <si>
-    <t>QF-4E</t>
-  </si>
-  <si>
     <t>weapons.containers.{MB339_ANM3_R}</t>
   </si>
   <si>
-    <t>RQ-1A Predator</t>
-  </si>
-  <si>
     <t>weapons.containers.{MB339_DEFA553_L}</t>
   </si>
   <si>
-    <t>S-3B</t>
-  </si>
-  <si>
     <t>weapons.containers.{MB339_DEFA553_R}</t>
   </si>
   <si>
     <t>weapons.containers.{MIG21_SMOKE_RED}</t>
   </si>
   <si>
-    <t>S-3B Tanker</t>
-  </si>
-  <si>
     <t>weapons.containers.{MIG21_SMOKE_WHITE}</t>
   </si>
   <si>
-    <t>SA342L</t>
-  </si>
-  <si>
     <t>weapons.containers.{PK-3}</t>
   </si>
   <si>
     <t>weapons.containers.{RKL609_L}</t>
   </si>
   <si>
-    <t>SA342M</t>
-  </si>
-  <si>
     <t>weapons.containers.{RKL609_R}</t>
   </si>
   <si>
     <t>weapons.containers.{SA342_M134_SIDE_R}</t>
   </si>
   <si>
-    <t>SA342Minigun</t>
-  </si>
-  <si>
     <t>weapons.containers.{SMOKE_WHITE}</t>
   </si>
   <si>
     <t>weapons.containers.{SUU_23_POD}</t>
   </si>
   <si>
-    <t>SA342Mistral</t>
-  </si>
-  <si>
     <t>weapons.containers.{US_M10_SMOKE_TANK_BLUE}</t>
   </si>
   <si>
@@ -1402,9 +1480,6 @@
     <t>weapons.containers.{US_M10_SMOKE_TANK_ORANGE}</t>
   </si>
   <si>
-    <t>SH-3W</t>
-  </si>
-  <si>
     <t>weapons.containers.{US_M10_SMOKE_TANK_RED}</t>
   </si>
   <si>
@@ -1414,9 +1489,6 @@
     <t>weapons.containers.{US_M10_SMOKE_TANK_YELLOW}</t>
   </si>
   <si>
-    <t>SH-60B</t>
-  </si>
-  <si>
     <t>weapons.droptanks.1100L Tank</t>
   </si>
   <si>
@@ -1426,147 +1498,96 @@
     <t>weapons.droptanks.800L Tank</t>
   </si>
   <si>
-    <t>SpitfireLFMkIX</t>
-  </si>
-  <si>
     <t>weapons.droptanks.800L Tank Empty</t>
   </si>
   <si>
     <t>weapons.droptanks.AV8BNA_AERO1D</t>
   </si>
   <si>
-    <t>SpitfireLFMkIXCW</t>
-  </si>
-  <si>
     <t>weapons.droptanks.AV8BNA_AERO1D_EMPTY</t>
   </si>
   <si>
     <t>weapons.droptanks.C130J_Ext_Tank_L</t>
   </si>
   <si>
-    <t>Su-17M4</t>
-  </si>
-  <si>
     <t>weapons.droptanks.C130J_Ext_Tank_R</t>
   </si>
   <si>
-    <t>Su-24M</t>
-  </si>
-  <si>
     <t>weapons.droptanks.CHAP_TigerUHT_fueltank</t>
   </si>
   <si>
     <t>weapons.droptanks.Drop tank 75gal</t>
   </si>
   <si>
-    <t>Su-24MR</t>
-  </si>
-  <si>
     <t>weapons.droptanks.Drop_Tank_300_Liter</t>
   </si>
   <si>
     <t>weapons.droptanks.F-15E_Drop_Tank</t>
   </si>
   <si>
-    <t>Su-25</t>
-  </si>
-  <si>
     <t>weapons.droptanks.F-15E_Drop_Tank_Empty</t>
   </si>
   <si>
     <t>weapons.droptanks.F-16-PTB-N2</t>
   </si>
   <si>
-    <t>Su-25T</t>
-  </si>
-  <si>
     <t>weapons.droptanks.F15-PTB</t>
   </si>
   <si>
     <t>weapons.droptanks.F4-BAK-C</t>
   </si>
   <si>
-    <t>Su-25TM</t>
-  </si>
-  <si>
     <t>weapons.droptanks.F4-BAK-L</t>
   </si>
   <si>
     <t>weapons.droptanks.F4U-1D_Drop_Tank_Aux</t>
   </si>
   <si>
-    <t>Su-27</t>
-  </si>
-  <si>
     <t>weapons.droptanks.F4U-1D_Drop_Tank_Mk5</t>
   </si>
   <si>
     <t>weapons.droptanks.F4U-1D_Drop_Tank_Mk6</t>
   </si>
   <si>
-    <t>Su-30</t>
-  </si>
-  <si>
     <t>weapons.droptanks.FPU_8A</t>
   </si>
   <si>
     <t>weapons.droptanks.FT600</t>
   </si>
   <si>
-    <t>Su-33</t>
-  </si>
-  <si>
     <t>weapons.droptanks.FW-190_Fuel-Tank</t>
   </si>
   <si>
     <t>weapons.droptanks.FuelTank_150L</t>
   </si>
   <si>
-    <t>Su-34</t>
-  </si>
-  <si>
     <t>weapons.droptanks.FuelTank_350L</t>
   </si>
   <si>
     <t>weapons.droptanks.GD_F100_TANK_200</t>
   </si>
   <si>
-    <t>TF-51D</t>
-  </si>
-  <si>
     <t>weapons.droptanks.GD_F100_TANK_275_L</t>
   </si>
   <si>
     <t>weapons.droptanks.GD_F100_TANK_275_R</t>
   </si>
   <si>
-    <t>Tornado GR4</t>
-  </si>
-  <si>
     <t>weapons.droptanks.GD_F100_TANK_335_L</t>
   </si>
   <si>
     <t>weapons.droptanks.GD_F100_TANK_335_R</t>
   </si>
   <si>
-    <t>Tornado IDS</t>
-  </si>
-  <si>
     <t>weapons.droptanks.GD_F100_TANK_450</t>
   </si>
   <si>
     <t>weapons.droptanks.HB_A6E_AERO1D</t>
   </si>
   <si>
-    <t>Tu-142</t>
-  </si>
-  <si>
     <t>weapons.droptanks.HB_A6E_AERO1D_EMPTY</t>
   </si>
   <si>
-    <t>Tu-160</t>
-  </si>
-  <si>
     <t>weapons.droptanks.HB_A6E_D704</t>
   </si>
   <si>
@@ -1576,61 +1597,40 @@
     <t>weapons.droptanks.HB_F-4E_EXT_Center_Fuel_Tank_EMPTY</t>
   </si>
   <si>
-    <t>Tu-22M3</t>
-  </si>
-  <si>
     <t>weapons.droptanks.HB_F-4E_EXT_WingTank</t>
   </si>
   <si>
     <t>weapons.droptanks.HB_F-4E_EXT_WingTank_EMPTY</t>
   </si>
   <si>
-    <t>Tu-95MS</t>
-  </si>
-  <si>
     <t>weapons.droptanks.HB_F-4E_EXT_WingTank_R</t>
   </si>
   <si>
     <t>weapons.droptanks.HB_F-4E_EXT_WingTank_R_EMPTY</t>
   </si>
   <si>
-    <t>UH-1H</t>
-  </si>
-  <si>
     <t>weapons.droptanks.HB_F14_EXT_DROPTANK</t>
   </si>
   <si>
     <t>weapons.droptanks.HB_F14_EXT_DROPTANK_EMPTY</t>
   </si>
   <si>
-    <t>UH-60A</t>
-  </si>
-  <si>
     <t>weapons.droptanks.HB_HIGH_PERFORMANCE_CENTERLINE_600_GAL</t>
   </si>
   <si>
     <t>weapons.droptanks.LNS_VIG_XTANK</t>
   </si>
   <si>
-    <t>WingLoong-I</t>
-  </si>
-  <si>
     <t>weapons.droptanks.M2000-PTB</t>
   </si>
   <si>
     <t>weapons.droptanks.M2KC_02_RPL541</t>
   </si>
   <si>
-    <t>Yak-40</t>
-  </si>
-  <si>
     <t>weapons.droptanks.M2KC_02_RPL541_EMPTY</t>
   </si>
   <si>
     <t>weapons.droptanks.M2KC_08_RPL541</t>
-  </si>
-  <si>
-    <t>Yak-52</t>
   </si>
   <si>
     <t>weapons.droptanks.M2KC_08_RPL541_EMPTY</t>
@@ -2837,7 +2837,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2">
         <v>0.0</v>
@@ -2845,7 +2845,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2">
         <v>0.0</v>
@@ -2853,7 +2853,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2">
         <v>0.0</v>
@@ -2861,7 +2861,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2">
         <v>0.0</v>
@@ -2869,7 +2869,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2">
         <v>0.0</v>
@@ -2877,7 +2877,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2">
         <v>0.0</v>
@@ -2893,7 +2893,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2">
         <v>0.0</v>
@@ -2901,7 +2901,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B11" s="2">
         <v>0.0</v>
@@ -2909,7 +2909,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B12" s="2">
         <v>0.0</v>
@@ -2917,7 +2917,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2">
         <v>0.0</v>
@@ -2925,7 +2925,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B14" s="2">
         <v>0.0</v>
@@ -2933,7 +2933,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B15" s="2">
         <v>0.0</v>
@@ -2941,7 +2941,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B16" s="2">
         <v>0.0</v>
@@ -2949,7 +2949,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2">
         <v>0.0</v>
@@ -2957,7 +2957,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2">
         <v>0.0</v>
@@ -2965,7 +2965,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B19" s="2">
         <v>0.0</v>
@@ -2973,7 +2973,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2">
         <v>0.0</v>
@@ -2981,7 +2981,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B21" s="2">
         <v>0.0</v>
@@ -2989,7 +2989,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B22" s="2">
         <v>0.0</v>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="B23" s="2">
         <v>0.0</v>
@@ -3005,7 +3005,7 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="B24" s="2">
         <v>0.0</v>
@@ -3013,7 +3013,7 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="B25" s="2">
         <v>0.0</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="B26" s="2">
         <v>0.0</v>
@@ -3029,7 +3029,7 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="B27" s="2">
         <v>0.0</v>
@@ -3037,7 +3037,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="B28" s="2">
         <v>0.0</v>
@@ -3045,7 +3045,7 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="B29" s="2">
         <v>0.0</v>
@@ -3053,7 +3053,7 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="B30" s="2">
         <v>0.0</v>
@@ -3061,7 +3061,7 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="B31" s="2">
         <v>0.0</v>
@@ -3069,7 +3069,7 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="B32" s="2">
         <v>0.0</v>
@@ -3077,7 +3077,7 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="B33" s="2">
         <v>0.0</v>
@@ -3085,7 +3085,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="B34" s="2">
         <v>0.0</v>
@@ -3093,7 +3093,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="B35" s="2">
         <v>0.0</v>
@@ -3101,7 +3101,7 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="B36" s="2">
         <v>0.0</v>
@@ -3109,7 +3109,7 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="B37" s="2">
         <v>0.0</v>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="B38" s="4">
         <v>0.0</v>
@@ -3149,7 +3149,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="B39" s="2">
         <v>0.0</v>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>150</v>
+        <v>93</v>
       </c>
       <c r="B40" s="2">
         <v>0.0</v>
@@ -3165,7 +3165,7 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="B41" s="2">
         <v>0.0</v>
@@ -3173,7 +3173,7 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="B42" s="2">
         <v>0.0</v>
@@ -3181,7 +3181,7 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="B43" s="2">
         <v>0.0</v>
@@ -3189,7 +3189,7 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="B44" s="2">
         <v>0.0</v>
@@ -3197,7 +3197,7 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="B45" s="2">
         <v>0.0</v>
@@ -3205,7 +3205,7 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>168</v>
+        <v>106</v>
       </c>
       <c r="B46" s="2">
         <v>0.0</v>
@@ -3213,7 +3213,7 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>171</v>
+        <v>109</v>
       </c>
       <c r="B47" s="2">
         <v>0.0</v>
@@ -3221,7 +3221,7 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>174</v>
+        <v>111</v>
       </c>
       <c r="B48" s="2">
         <v>0.0</v>
@@ -3229,7 +3229,7 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>177</v>
+        <v>113</v>
       </c>
       <c r="B49" s="2">
         <v>0.0</v>
@@ -3237,7 +3237,7 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>181</v>
+        <v>115</v>
       </c>
       <c r="B50" s="2">
         <v>0.0</v>
@@ -3245,7 +3245,7 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>184</v>
+        <v>118</v>
       </c>
       <c r="B51" s="2">
         <v>0.0</v>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>188</v>
+        <v>120</v>
       </c>
       <c r="B52" s="2">
         <v>0.0</v>
@@ -3261,7 +3261,7 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>190</v>
+        <v>122</v>
       </c>
       <c r="B53" s="2">
         <v>0.0</v>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="B54" s="2">
         <v>0.0</v>
@@ -3277,7 +3277,7 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>194</v>
+        <v>127</v>
       </c>
       <c r="B55" s="2">
         <v>0.0</v>
@@ -3285,7 +3285,7 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>197</v>
+        <v>130</v>
       </c>
       <c r="B56" s="2">
         <v>0.0</v>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>200</v>
+        <v>132</v>
       </c>
       <c r="B57" s="2">
         <v>0.0</v>
@@ -3301,7 +3301,7 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>203</v>
+        <v>135</v>
       </c>
       <c r="B58" s="2">
         <v>0.0</v>
@@ -3309,7 +3309,7 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>206</v>
+        <v>138</v>
       </c>
       <c r="B59" s="2">
         <v>0.0</v>
@@ -3317,7 +3317,7 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>208</v>
+        <v>140</v>
       </c>
       <c r="B60" s="2">
         <v>0.0</v>
@@ -3325,7 +3325,7 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="B61" s="2">
         <v>0.0</v>
@@ -3333,7 +3333,7 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>212</v>
+        <v>146</v>
       </c>
       <c r="B62" s="2">
         <v>0.0</v>
@@ -3341,7 +3341,7 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>215</v>
+        <v>148</v>
       </c>
       <c r="B63" s="2">
         <v>0.0</v>
@@ -3349,7 +3349,7 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>218</v>
+        <v>150</v>
       </c>
       <c r="B64" s="2">
         <v>0.0</v>
@@ -3357,7 +3357,7 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>221</v>
+        <v>152</v>
       </c>
       <c r="B65" s="2">
         <v>0.0</v>
@@ -3365,7 +3365,7 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>224</v>
+        <v>154</v>
       </c>
       <c r="B66" s="2">
         <v>0.0</v>
@@ -3373,7 +3373,7 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>227</v>
+        <v>157</v>
       </c>
       <c r="B67" s="2">
         <v>0.0</v>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>229</v>
+        <v>159</v>
       </c>
       <c r="B68" s="2">
         <v>0.0</v>
@@ -3389,7 +3389,7 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>232</v>
+        <v>161</v>
       </c>
       <c r="B69" s="2">
         <v>0.0</v>
@@ -3397,7 +3397,7 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>235</v>
+        <v>164</v>
       </c>
       <c r="B70" s="2">
         <v>0.0</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>238</v>
+        <v>166</v>
       </c>
       <c r="B71" s="2">
         <v>0.0</v>
@@ -3413,7 +3413,7 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>241</v>
+        <v>168</v>
       </c>
       <c r="B72" s="2">
         <v>0.0</v>
@@ -3421,7 +3421,7 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>244</v>
+        <v>170</v>
       </c>
       <c r="B73" s="2">
         <v>0.0</v>
@@ -3429,7 +3429,7 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>247</v>
+        <v>172</v>
       </c>
       <c r="B74" s="2">
         <v>0.0</v>
@@ -3437,7 +3437,7 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>250</v>
+        <v>174</v>
       </c>
       <c r="B75" s="2">
         <v>0.0</v>
@@ -3445,7 +3445,7 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>266</v>
+        <v>177</v>
       </c>
       <c r="B76" s="2">
         <v>0.0</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>269</v>
+        <v>179</v>
       </c>
       <c r="B77" s="2">
         <v>0.0</v>
@@ -3461,7 +3461,7 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>273</v>
+        <v>181</v>
       </c>
       <c r="B78" s="2">
         <v>0.0</v>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>276</v>
+        <v>183</v>
       </c>
       <c r="B79" s="2">
         <v>0.0</v>
@@ -3477,7 +3477,7 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>279</v>
+        <v>185</v>
       </c>
       <c r="B80" s="2">
         <v>0.0</v>
@@ -3485,7 +3485,7 @@
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>282</v>
+        <v>188</v>
       </c>
       <c r="B81" s="2">
         <v>0.0</v>
@@ -3493,7 +3493,7 @@
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>290</v>
+        <v>190</v>
       </c>
       <c r="B82" s="2">
         <v>0.0</v>
@@ -3501,7 +3501,7 @@
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>293</v>
+        <v>192</v>
       </c>
       <c r="B83" s="2">
         <v>0.0</v>
@@ -3509,7 +3509,7 @@
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>296</v>
+        <v>196</v>
       </c>
       <c r="B84" s="2">
         <v>0.0</v>
@@ -3517,7 +3517,7 @@
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>299</v>
+        <v>199</v>
       </c>
       <c r="B85" s="2">
         <v>0.0</v>
@@ -3525,7 +3525,7 @@
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>302</v>
+        <v>202</v>
       </c>
       <c r="B86" s="2">
         <v>0.0</v>
@@ -3533,7 +3533,7 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>305</v>
+        <v>204</v>
       </c>
       <c r="B87" s="2">
         <v>0.0</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>308</v>
+        <v>206</v>
       </c>
       <c r="B88" s="2">
         <v>0.0</v>
@@ -3549,7 +3549,7 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>311</v>
+        <v>209</v>
       </c>
       <c r="B89" s="2">
         <v>0.0</v>
@@ -3557,7 +3557,7 @@
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>314</v>
+        <v>211</v>
       </c>
       <c r="B90" s="2">
         <v>0.0</v>
@@ -3565,7 +3565,7 @@
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>318</v>
+        <v>213</v>
       </c>
       <c r="B91" s="2">
         <v>0.0</v>
@@ -3573,7 +3573,7 @@
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>321</v>
+        <v>216</v>
       </c>
       <c r="B92" s="2">
         <v>0.0</v>
@@ -3581,7 +3581,7 @@
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>324</v>
+        <v>218</v>
       </c>
       <c r="B93" s="2">
         <v>0.0</v>
@@ -3589,7 +3589,7 @@
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>327</v>
+        <v>220</v>
       </c>
       <c r="B94" s="2">
         <v>0.0</v>
@@ -3597,7 +3597,7 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>329</v>
+        <v>222</v>
       </c>
       <c r="B95" s="2">
         <v>0.0</v>
@@ -3605,7 +3605,7 @@
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>332</v>
+        <v>225</v>
       </c>
       <c r="B96" s="2">
         <v>0.0</v>
@@ -3613,7 +3613,7 @@
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>334</v>
+        <v>229</v>
       </c>
       <c r="B97" s="2">
         <v>0.0</v>
@@ -3621,7 +3621,7 @@
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>336</v>
+        <v>231</v>
       </c>
       <c r="B98" s="2">
         <v>0.0</v>
@@ -3629,7 +3629,7 @@
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>339</v>
+        <v>234</v>
       </c>
       <c r="B99" s="2">
         <v>0.0</v>
@@ -3637,7 +3637,7 @@
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>342</v>
+        <v>236</v>
       </c>
       <c r="B100" s="2">
         <v>0.0</v>
@@ -3645,7 +3645,7 @@
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="1" t="s">
-        <v>345</v>
+        <v>238</v>
       </c>
       <c r="B101" s="2">
         <v>0.0</v>
@@ -3653,7 +3653,7 @@
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>348</v>
+        <v>241</v>
       </c>
       <c r="B102" s="2">
         <v>0.0</v>
@@ -3661,7 +3661,7 @@
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="B103" s="2">
         <v>0.0</v>
@@ -3669,7 +3669,7 @@
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="1" t="s">
-        <v>356</v>
+        <v>247</v>
       </c>
       <c r="B104" s="2">
         <v>0.0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>358</v>
+        <v>250</v>
       </c>
       <c r="B105" s="2">
         <v>0.0</v>
@@ -3685,7 +3685,7 @@
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>361</v>
+        <v>253</v>
       </c>
       <c r="B106" s="2">
         <v>0.0</v>
@@ -3693,7 +3693,7 @@
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="1" t="s">
-        <v>364</v>
+        <v>255</v>
       </c>
       <c r="B107" s="2">
         <v>0.0</v>
@@ -3701,7 +3701,7 @@
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="1" t="s">
-        <v>367</v>
+        <v>258</v>
       </c>
       <c r="B108" s="2">
         <v>0.0</v>
@@ -3709,7 +3709,7 @@
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="1" t="s">
-        <v>371</v>
+        <v>261</v>
       </c>
       <c r="B109" s="2">
         <v>0.0</v>
@@ -3717,7 +3717,7 @@
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="1" t="s">
-        <v>374</v>
+        <v>264</v>
       </c>
       <c r="B110" s="2">
         <v>0.0</v>
@@ -3725,7 +3725,7 @@
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="1" t="s">
-        <v>377</v>
+        <v>266</v>
       </c>
       <c r="B111" s="2">
         <v>0.0</v>
@@ -3733,7 +3733,7 @@
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="1" t="s">
-        <v>380</v>
+        <v>269</v>
       </c>
       <c r="B112" s="2">
         <v>0.0</v>
@@ -3741,7 +3741,7 @@
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="1" t="s">
-        <v>383</v>
+        <v>272</v>
       </c>
       <c r="B113" s="2">
         <v>0.0</v>
@@ -3749,7 +3749,7 @@
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="1" t="s">
-        <v>385</v>
+        <v>274</v>
       </c>
       <c r="B114" s="2">
         <v>0.0</v>
@@ -3757,7 +3757,7 @@
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="1" t="s">
-        <v>387</v>
+        <v>277</v>
       </c>
       <c r="B115" s="2">
         <v>0.0</v>
@@ -3765,7 +3765,7 @@
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="1" t="s">
-        <v>390</v>
+        <v>280</v>
       </c>
       <c r="B116" s="2">
         <v>0.0</v>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="1" t="s">
-        <v>393</v>
+        <v>283</v>
       </c>
       <c r="B117" s="2">
         <v>0.0</v>
@@ -3781,7 +3781,7 @@
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="1" t="s">
-        <v>396</v>
+        <v>285</v>
       </c>
       <c r="B118" s="2">
         <v>0.0</v>
@@ -3789,7 +3789,7 @@
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="1" t="s">
-        <v>398</v>
+        <v>288</v>
       </c>
       <c r="B119" s="2">
         <v>0.0</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="1" t="s">
-        <v>399</v>
+        <v>291</v>
       </c>
       <c r="B120" s="2">
         <v>0.0</v>
@@ -3805,7 +3805,7 @@
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="1" t="s">
-        <v>402</v>
+        <v>293</v>
       </c>
       <c r="B121" s="2">
         <v>0.0</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="1" t="s">
-        <v>405</v>
+        <v>296</v>
       </c>
       <c r="B122" s="2">
         <v>0.0</v>
@@ -3821,7 +3821,7 @@
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="1" t="s">
-        <v>408</v>
+        <v>299</v>
       </c>
       <c r="B123" s="2">
         <v>0.0</v>
@@ -3829,7 +3829,7 @@
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="1" t="s">
-        <v>411</v>
+        <v>302</v>
       </c>
       <c r="B124" s="2">
         <v>0.0</v>
@@ -3837,7 +3837,7 @@
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="1" t="s">
-        <v>414</v>
+        <v>304</v>
       </c>
       <c r="B125" s="2">
         <v>0.0</v>
@@ -3845,7 +3845,7 @@
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="1" t="s">
-        <v>417</v>
+        <v>307</v>
       </c>
       <c r="B126" s="2">
         <v>0.0</v>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="1" t="s">
-        <v>420</v>
+        <v>310</v>
       </c>
       <c r="B127" s="2">
         <v>0.0</v>
@@ -3861,7 +3861,7 @@
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="1" t="s">
-        <v>425</v>
+        <v>312</v>
       </c>
       <c r="B128" s="2">
         <v>0.0</v>
@@ -3869,7 +3869,7 @@
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="1" t="s">
-        <v>427</v>
+        <v>315</v>
       </c>
       <c r="B129" s="2">
         <v>0.0</v>
@@ -3877,7 +3877,7 @@
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="1" t="s">
-        <v>430</v>
+        <v>317</v>
       </c>
       <c r="B130" s="2">
         <v>0.0</v>
@@ -3885,7 +3885,7 @@
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="1" t="s">
-        <v>433</v>
+        <v>320</v>
       </c>
       <c r="B131" s="2">
         <v>0.0</v>
@@ -3893,7 +3893,7 @@
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="1" t="s">
-        <v>436</v>
+        <v>322</v>
       </c>
       <c r="B132" s="2">
         <v>0.0</v>
@@ -3901,7 +3901,7 @@
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="1" t="s">
-        <v>439</v>
+        <v>324</v>
       </c>
       <c r="B133" s="2">
         <v>0.0</v>
@@ -3909,7 +3909,7 @@
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="1" t="s">
-        <v>441</v>
+        <v>326</v>
       </c>
       <c r="B134" s="2">
         <v>0.0</v>
@@ -3917,7 +3917,7 @@
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="1" t="s">
-        <v>443</v>
+        <v>328</v>
       </c>
       <c r="B135" s="2">
         <v>0.0</v>
@@ -3925,7 +3925,7 @@
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="1" t="s">
-        <v>446</v>
+        <v>330</v>
       </c>
       <c r="B136" s="2">
         <v>0.0</v>
@@ -3933,7 +3933,7 @@
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="1" t="s">
-        <v>448</v>
+        <v>332</v>
       </c>
       <c r="B137" s="2">
         <v>0.0</v>
@@ -3941,7 +3941,7 @@
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="1" t="s">
-        <v>451</v>
+        <v>334</v>
       </c>
       <c r="B138" s="2">
         <v>0.0</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="1" t="s">
-        <v>454</v>
+        <v>336</v>
       </c>
       <c r="B139" s="2">
         <v>0.0</v>
@@ -3957,7 +3957,7 @@
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="1" t="s">
-        <v>457</v>
+        <v>338</v>
       </c>
       <c r="B140" s="2">
         <v>0.0</v>
@@ -3965,7 +3965,7 @@
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="1" t="s">
-        <v>461</v>
+        <v>340</v>
       </c>
       <c r="B141" s="2">
         <v>0.0</v>
@@ -3973,7 +3973,7 @@
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="1" t="s">
-        <v>465</v>
+        <v>343</v>
       </c>
       <c r="B142" s="2">
         <v>0.0</v>
@@ -3981,7 +3981,7 @@
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="1" t="s">
-        <v>469</v>
+        <v>346</v>
       </c>
       <c r="B143" s="2">
         <v>0.0</v>
@@ -3989,7 +3989,7 @@
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="1" t="s">
-        <v>472</v>
+        <v>348</v>
       </c>
       <c r="B144" s="2">
         <v>0.0</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="1" t="s">
-        <v>475</v>
+        <v>351</v>
       </c>
       <c r="B145" s="2">
         <v>0.0</v>
@@ -4005,7 +4005,7 @@
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="1" t="s">
-        <v>477</v>
+        <v>353</v>
       </c>
       <c r="B146" s="2">
         <v>0.0</v>
@@ -4013,7 +4013,7 @@
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="1" t="s">
-        <v>480</v>
+        <v>356</v>
       </c>
       <c r="B147" s="2">
         <v>0.0</v>
@@ -4021,7 +4021,7 @@
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="1" t="s">
-        <v>483</v>
+        <v>359</v>
       </c>
       <c r="B148" s="2">
         <v>0.0</v>
@@ -4029,7 +4029,7 @@
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="1" t="s">
-        <v>486</v>
+        <v>361</v>
       </c>
       <c r="B149" s="2">
         <v>0.0</v>
@@ -4037,7 +4037,7 @@
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="1" t="s">
-        <v>489</v>
+        <v>364</v>
       </c>
       <c r="B150" s="2">
         <v>0.0</v>
@@ -4045,7 +4045,7 @@
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="1" t="s">
-        <v>492</v>
+        <v>366</v>
       </c>
       <c r="B151" s="2">
         <v>0.0</v>
@@ -4053,7 +4053,7 @@
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="1" t="s">
-        <v>495</v>
+        <v>368</v>
       </c>
       <c r="B152" s="2">
         <v>0.0</v>
@@ -4061,7 +4061,7 @@
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="1" t="s">
-        <v>498</v>
+        <v>371</v>
       </c>
       <c r="B153" s="2">
         <v>0.0</v>
@@ -4069,7 +4069,7 @@
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="1" t="s">
-        <v>501</v>
+        <v>373</v>
       </c>
       <c r="B154" s="2">
         <v>0.0</v>
@@ -4077,7 +4077,7 @@
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="1" t="s">
-        <v>504</v>
+        <v>376</v>
       </c>
       <c r="B155" s="2">
         <v>0.0</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="1" t="s">
-        <v>507</v>
+        <v>379</v>
       </c>
       <c r="B156" s="2">
         <v>0.0</v>
@@ -4093,7 +4093,7 @@
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="1" t="s">
-        <v>510</v>
+        <v>381</v>
       </c>
       <c r="B157" s="2">
         <v>0.0</v>
@@ -4101,7 +4101,7 @@
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="1" t="s">
-        <v>513</v>
+        <v>384</v>
       </c>
       <c r="B158" s="2">
         <v>0.0</v>
@@ -4109,7 +4109,7 @@
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="1" t="s">
-        <v>515</v>
+        <v>387</v>
       </c>
       <c r="B159" s="2">
         <v>0.0</v>
@@ -4117,7 +4117,7 @@
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="1" t="s">
-        <v>519</v>
+        <v>389</v>
       </c>
       <c r="B160" s="2">
         <v>0.0</v>
@@ -4125,7 +4125,7 @@
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="1" t="s">
-        <v>522</v>
+        <v>392</v>
       </c>
       <c r="B161" s="2">
         <v>0.0</v>
@@ -4133,7 +4133,7 @@
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="1" t="s">
-        <v>525</v>
+        <v>394</v>
       </c>
       <c r="B162" s="2">
         <v>0.0</v>
@@ -4141,7 +4141,7 @@
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="1" t="s">
-        <v>528</v>
+        <v>397</v>
       </c>
       <c r="B163" s="2">
         <v>0.0</v>
@@ -4149,7 +4149,7 @@
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="1" t="s">
-        <v>531</v>
+        <v>400</v>
       </c>
       <c r="B164" s="2">
         <v>0.0</v>
@@ -4157,7 +4157,7 @@
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="1" t="s">
-        <v>534</v>
+        <v>403</v>
       </c>
       <c r="B165" s="2">
         <v>0.0</v>
@@ -4165,7 +4165,7 @@
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="1" t="s">
-        <v>537</v>
+        <v>406</v>
       </c>
       <c r="B166" s="2">
         <v>0.0</v>
@@ -5037,7 +5037,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2">
         <v>0.0</v>
@@ -5045,7 +5045,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2">
         <v>0.0</v>
@@ -5053,7 +5053,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2">
         <v>0.0</v>
@@ -5061,7 +5061,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2">
         <v>0.0</v>
@@ -5069,7 +5069,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2">
         <v>0.0</v>
@@ -5077,7 +5077,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2">
         <v>0.0</v>
@@ -5085,7 +5085,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2">
         <v>0.0</v>
@@ -5093,7 +5093,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2">
         <v>0.0</v>
@@ -5101,7 +5101,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2">
         <v>0.0</v>
@@ -5109,7 +5109,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B11" s="2">
         <v>0.0</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2">
         <v>0.0</v>
@@ -5125,7 +5125,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2">
         <v>0.0</v>
@@ -5133,7 +5133,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2">
         <v>0.0</v>
@@ -5141,7 +5141,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B15" s="2">
         <v>0.0</v>
@@ -5149,7 +5149,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="2">
         <v>0.0</v>
@@ -5157,7 +5157,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B17" s="2">
         <v>0.0</v>
@@ -5181,7 +5181,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2">
         <v>0.0</v>
@@ -5189,7 +5189,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B21" s="2">
         <v>0.0</v>
@@ -5197,7 +5197,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B22" s="2">
         <v>0.0</v>
@@ -5205,7 +5205,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B23" s="2">
         <v>0.0</v>
@@ -5213,7 +5213,7 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B24" s="2">
         <v>0.0</v>
@@ -5221,7 +5221,7 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B25" s="2">
         <v>0.0</v>
@@ -5229,7 +5229,7 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B26" s="2">
         <v>0.0</v>
@@ -5237,7 +5237,7 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B27" s="2">
         <v>0.0</v>
@@ -5245,7 +5245,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B28" s="2">
         <v>0.0</v>
@@ -5253,7 +5253,7 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B29" s="2">
         <v>0.0</v>
@@ -5261,7 +5261,7 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B30" s="2">
         <v>0.0</v>
@@ -5269,7 +5269,7 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B31" s="2">
         <v>0.0</v>
@@ -5277,7 +5277,7 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B32" s="2">
         <v>0.0</v>
@@ -5285,7 +5285,7 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B33" s="2">
         <v>0.0</v>
@@ -5293,7 +5293,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B34" s="2">
         <v>0.0</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B35" s="2">
         <v>0.0</v>
@@ -5309,7 +5309,7 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B36" s="2">
         <v>0.0</v>
@@ -5317,7 +5317,7 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="B37" s="2">
         <v>0.0</v>
@@ -5325,7 +5325,7 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B38" s="2">
         <v>0.0</v>
@@ -5333,7 +5333,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="B39" s="2">
         <v>0.0</v>
@@ -5341,7 +5341,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B40" s="2">
         <v>0.0</v>
@@ -5349,7 +5349,7 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="B41" s="2">
         <v>0.0</v>
@@ -5357,7 +5357,7 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="B42" s="2">
         <v>0.0</v>
@@ -5365,7 +5365,7 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B43" s="2">
         <v>0.0</v>
@@ -5373,7 +5373,7 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="B44" s="2">
         <v>0.0</v>
@@ -5381,7 +5381,7 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="B45" s="2">
         <v>0.0</v>
@@ -5389,7 +5389,7 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="B46" s="2">
         <v>0.0</v>
@@ -5397,7 +5397,7 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="B47" s="2">
         <v>0.0</v>
@@ -5405,7 +5405,7 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="B48" s="2">
         <v>0.0</v>
@@ -5413,7 +5413,7 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="B49" s="2">
         <v>0.0</v>
@@ -5421,7 +5421,7 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B50" s="2">
         <v>0.0</v>
@@ -5429,7 +5429,7 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B51" s="2">
         <v>0.0</v>
@@ -5437,7 +5437,7 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="B52" s="2">
         <v>0.0</v>
@@ -5445,7 +5445,7 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B53" s="2">
         <v>0.0</v>
@@ -5453,7 +5453,7 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B54" s="2">
         <v>0.0</v>
@@ -5461,7 +5461,7 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="B55" s="2">
         <v>0.0</v>
@@ -5469,7 +5469,7 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B56" s="2">
         <v>0.0</v>
@@ -5477,7 +5477,7 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B57" s="2">
         <v>0.0</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B58" s="2">
         <v>0.0</v>
@@ -5493,7 +5493,7 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="B59" s="2">
         <v>0.0</v>
@@ -5501,7 +5501,7 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="B60" s="2">
         <v>0.0</v>
@@ -5509,7 +5509,7 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="B61" s="2">
         <v>0.0</v>
@@ -5517,7 +5517,7 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="B62" s="2">
         <v>0.0</v>
@@ -5525,7 +5525,7 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="B63" s="2">
         <v>0.0</v>
@@ -5533,7 +5533,7 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="B64" s="2">
         <v>0.0</v>
@@ -5541,7 +5541,7 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="B65" s="2">
         <v>0.0</v>
@@ -5549,7 +5549,7 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="B66" s="2">
         <v>0.0</v>
@@ -5557,7 +5557,7 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="B67" s="2">
         <v>0.0</v>
@@ -5565,7 +5565,7 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="B68" s="2">
         <v>0.0</v>
@@ -5573,7 +5573,7 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="B69" s="2">
         <v>0.0</v>
@@ -5581,7 +5581,7 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="B70" s="2">
         <v>0.0</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="B71" s="2">
         <v>0.0</v>
@@ -5597,7 +5597,7 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B72" s="2">
         <v>0.0</v>
@@ -5605,7 +5605,7 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="B73" s="2">
         <v>0.0</v>
@@ -5613,7 +5613,7 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="B74" s="2">
         <v>0.0</v>
@@ -5621,7 +5621,7 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="B75" s="2">
         <v>0.0</v>
@@ -5629,7 +5629,7 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="B76" s="2">
         <v>0.0</v>
@@ -5637,7 +5637,7 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="B77" s="2">
         <v>0.0</v>
@@ -5645,7 +5645,7 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="B78" s="2">
         <v>0.0</v>
@@ -5653,7 +5653,7 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="B79" s="2">
         <v>0.0</v>
@@ -5661,7 +5661,7 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="B80" s="2">
         <v>0.0</v>
@@ -5669,7 +5669,7 @@
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="B81" s="2">
         <v>0.0</v>
@@ -5677,7 +5677,7 @@
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="B82" s="2">
         <v>0.0</v>
@@ -5685,7 +5685,7 @@
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="B83" s="2">
         <v>0.0</v>
@@ -5693,7 +5693,7 @@
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="B84" s="2">
         <v>0.0</v>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="B85" s="2">
         <v>0.0</v>
@@ -5709,7 +5709,7 @@
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="B86" s="2">
         <v>0.0</v>
@@ -5717,7 +5717,7 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="B87" s="2">
         <v>0.0</v>
@@ -5725,7 +5725,7 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="B88" s="2">
         <v>0.0</v>
@@ -5733,7 +5733,7 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="B89" s="2">
         <v>0.0</v>
@@ -5741,7 +5741,7 @@
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="B90" s="2">
         <v>0.0</v>
@@ -5749,7 +5749,7 @@
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="B91" s="2">
         <v>0.0</v>
@@ -5757,7 +5757,7 @@
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="B92" s="2">
         <v>0.0</v>
@@ -5765,7 +5765,7 @@
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="B93" s="2">
         <v>0.0</v>
@@ -5773,7 +5773,7 @@
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="B94" s="2">
         <v>0.0</v>
@@ -5781,7 +5781,7 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="B95" s="2">
         <v>0.0</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="B96" s="2">
         <v>0.0</v>
@@ -5797,7 +5797,7 @@
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="B97" s="2">
         <v>0.0</v>
@@ -5805,7 +5805,7 @@
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="B98" s="2">
         <v>0.0</v>
@@ -5813,7 +5813,7 @@
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="B99" s="2">
         <v>0.0</v>
@@ -5821,7 +5821,7 @@
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="B100" s="2">
         <v>0.0</v>
@@ -5829,7 +5829,7 @@
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="1" t="s">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="B101" s="2">
         <v>0.0</v>
@@ -5837,7 +5837,7 @@
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>143</v>
+        <v>184</v>
       </c>
       <c r="B102" s="2">
         <v>0.0</v>
@@ -5845,7 +5845,7 @@
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="B103" s="2">
         <v>0.0</v>
@@ -5853,7 +5853,7 @@
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="1" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="B104" s="2">
         <v>0.0</v>
@@ -5861,7 +5861,7 @@
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="B105" s="2">
         <v>0.0</v>
@@ -5869,7 +5869,7 @@
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="B106" s="2">
         <v>0.0</v>
@@ -5877,7 +5877,7 @@
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="1" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="B107" s="2">
         <v>0.0</v>
@@ -5885,7 +5885,7 @@
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="1" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="B108" s="2">
         <v>0.0</v>
@@ -5893,7 +5893,7 @@
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="1" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="B109" s="2">
         <v>0.0</v>
@@ -5901,7 +5901,7 @@
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="1" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="B110" s="2">
         <v>0.0</v>
@@ -5909,7 +5909,7 @@
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="1" t="s">
-        <v>155</v>
+        <v>198</v>
       </c>
       <c r="B111" s="2">
         <v>0.0</v>
@@ -5917,7 +5917,7 @@
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="1" t="s">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="B112" s="2">
         <v>0.0</v>
@@ -5925,7 +5925,7 @@
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="1" t="s">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="B113" s="2">
         <v>0.0</v>
@@ -5933,7 +5933,7 @@
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="1" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="B114" s="2">
         <v>0.0</v>
@@ -5941,7 +5941,7 @@
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="1" t="s">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="B115" s="2">
         <v>0.0</v>
@@ -5949,7 +5949,7 @@
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="1" t="s">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="B116" s="2">
         <v>0.0</v>
@@ -5957,7 +5957,7 @@
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="1" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
       <c r="B117" s="2">
         <v>0.0</v>
@@ -5965,7 +5965,7 @@
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="1" t="s">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="B118" s="2">
         <v>0.0</v>
@@ -5973,7 +5973,7 @@
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="1" t="s">
-        <v>167</v>
+        <v>212</v>
       </c>
       <c r="B119" s="2">
         <v>0.0</v>
@@ -5981,7 +5981,7 @@
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="1" t="s">
-        <v>169</v>
+        <v>214</v>
       </c>
       <c r="B120" s="2">
         <v>0.0</v>
@@ -5989,7 +5989,7 @@
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="1" t="s">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="B121" s="2">
         <v>0.0</v>
@@ -5997,7 +5997,7 @@
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="1" t="s">
-        <v>172</v>
+        <v>217</v>
       </c>
       <c r="B122" s="2">
         <v>0.0</v>
@@ -6005,7 +6005,7 @@
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="1" t="s">
-        <v>173</v>
+        <v>219</v>
       </c>
       <c r="B123" s="2">
         <v>0.0</v>
@@ -6013,7 +6013,7 @@
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="1" t="s">
-        <v>175</v>
+        <v>221</v>
       </c>
       <c r="B124" s="2">
         <v>0.0</v>
@@ -6021,7 +6021,7 @@
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="1" t="s">
-        <v>176</v>
+        <v>223</v>
       </c>
       <c r="B125" s="2">
         <v>0.0</v>
@@ -6029,7 +6029,7 @@
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="1" t="s">
-        <v>178</v>
+        <v>224</v>
       </c>
       <c r="B126" s="2">
         <v>0.0</v>
@@ -6037,7 +6037,7 @@
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="1" t="s">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="B127" s="2">
         <v>0.0</v>
@@ -6045,7 +6045,7 @@
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="1" t="s">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="B128" s="2">
         <v>0.0</v>
@@ -6053,7 +6053,7 @@
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="1" t="s">
-        <v>182</v>
+        <v>228</v>
       </c>
       <c r="B129" s="2">
         <v>0.0</v>
@@ -6061,7 +6061,7 @@
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="1" t="s">
-        <v>183</v>
+        <v>230</v>
       </c>
       <c r="B130" s="2">
         <v>0.0</v>
@@ -6069,7 +6069,7 @@
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="1" t="s">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="B131" s="2">
         <v>0.0</v>
@@ -6077,7 +6077,7 @@
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="1" t="s">
-        <v>186</v>
+        <v>233</v>
       </c>
       <c r="B132" s="2">
         <v>0.0</v>
@@ -6085,7 +6085,7 @@
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="1" t="s">
-        <v>187</v>
+        <v>235</v>
       </c>
       <c r="B133" s="2">
         <v>0.0</v>
@@ -6093,7 +6093,7 @@
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="1" t="s">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="B134" s="2">
         <v>0.0</v>
@@ -6101,7 +6101,7 @@
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="1" t="s">
-        <v>191</v>
+        <v>239</v>
       </c>
       <c r="B135" s="2">
         <v>0.0</v>
@@ -6109,7 +6109,7 @@
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="1" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="B136" s="2">
         <v>0.0</v>
@@ -6117,7 +6117,7 @@
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="1" t="s">
-        <v>195</v>
+        <v>242</v>
       </c>
       <c r="B137" s="2">
         <v>0.0</v>
@@ -6125,7 +6125,7 @@
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="1" t="s">
-        <v>196</v>
+        <v>243</v>
       </c>
       <c r="B138" s="2">
         <v>0.0</v>
@@ -6133,7 +6133,7 @@
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="1" t="s">
-        <v>198</v>
+        <v>245</v>
       </c>
       <c r="B139" s="2">
         <v>0.0</v>
@@ -6141,7 +6141,7 @@
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="1" t="s">
-        <v>199</v>
+        <v>246</v>
       </c>
       <c r="B140" s="2">
         <v>0.0</v>
@@ -6149,7 +6149,7 @@
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="1" t="s">
-        <v>201</v>
+        <v>248</v>
       </c>
       <c r="B141" s="2">
         <v>0.0</v>
@@ -6157,7 +6157,7 @@
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="1" t="s">
-        <v>202</v>
+        <v>249</v>
       </c>
       <c r="B142" s="2">
         <v>0.0</v>
@@ -6165,7 +6165,7 @@
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="1" t="s">
-        <v>204</v>
+        <v>251</v>
       </c>
       <c r="B143" s="2">
         <v>0.0</v>
@@ -6173,7 +6173,7 @@
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="1" t="s">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="B144" s="2">
         <v>0.0</v>
@@ -6181,7 +6181,7 @@
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="1" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="B145" s="2">
         <v>0.0</v>
@@ -6189,7 +6189,7 @@
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="1" t="s">
-        <v>209</v>
+        <v>256</v>
       </c>
       <c r="B146" s="2">
         <v>0.0</v>
@@ -6197,7 +6197,7 @@
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="1" t="s">
-        <v>211</v>
+        <v>257</v>
       </c>
       <c r="B147" s="2">
         <v>0.0</v>
@@ -6205,7 +6205,7 @@
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="1" t="s">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="B148" s="2">
         <v>0.0</v>
@@ -6213,7 +6213,7 @@
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="1" t="s">
-        <v>214</v>
+        <v>260</v>
       </c>
       <c r="B149" s="2">
         <v>0.0</v>
@@ -6221,7 +6221,7 @@
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="1" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="B150" s="2">
         <v>0.0</v>
@@ -6229,7 +6229,7 @@
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="1" t="s">
-        <v>217</v>
+        <v>263</v>
       </c>
       <c r="B151" s="2">
         <v>0.0</v>
@@ -6237,7 +6237,7 @@
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="1" t="s">
-        <v>219</v>
+        <v>265</v>
       </c>
       <c r="B152" s="2">
         <v>0.0</v>
@@ -6245,7 +6245,7 @@
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="1" t="s">
-        <v>220</v>
+        <v>267</v>
       </c>
       <c r="B153" s="2">
         <v>0.0</v>
@@ -6253,7 +6253,7 @@
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="1" t="s">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="B154" s="2">
         <v>0.0</v>
@@ -6261,7 +6261,7 @@
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="1" t="s">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="B155" s="2">
         <v>0.0</v>
@@ -6269,7 +6269,7 @@
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="1" t="s">
-        <v>225</v>
+        <v>271</v>
       </c>
       <c r="B156" s="2">
         <v>0.0</v>
@@ -6277,7 +6277,7 @@
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="1" t="s">
-        <v>226</v>
+        <v>273</v>
       </c>
       <c r="B157" s="2">
         <v>0.0</v>
@@ -6285,7 +6285,7 @@
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="1" t="s">
-        <v>228</v>
+        <v>275</v>
       </c>
       <c r="B158" s="2">
         <v>0.0</v>
@@ -6293,7 +6293,7 @@
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="1" t="s">
-        <v>230</v>
+        <v>276</v>
       </c>
       <c r="B159" s="2">
         <v>0.0</v>
@@ -6301,7 +6301,7 @@
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="1" t="s">
-        <v>231</v>
+        <v>278</v>
       </c>
       <c r="B160" s="2">
         <v>0.0</v>
@@ -6309,7 +6309,7 @@
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="1" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="B161" s="2">
         <v>0.0</v>
@@ -6317,7 +6317,7 @@
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="1" t="s">
-        <v>234</v>
+        <v>281</v>
       </c>
       <c r="B162" s="2">
         <v>0.0</v>
@@ -6325,7 +6325,7 @@
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="1" t="s">
-        <v>236</v>
+        <v>282</v>
       </c>
       <c r="B163" s="2">
         <v>0.0</v>
@@ -6333,7 +6333,7 @@
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="1" t="s">
-        <v>237</v>
+        <v>284</v>
       </c>
       <c r="B164" s="2">
         <v>0.0</v>
@@ -6341,7 +6341,7 @@
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="1" t="s">
-        <v>239</v>
+        <v>286</v>
       </c>
       <c r="B165" s="2">
         <v>0.0</v>
@@ -6349,7 +6349,7 @@
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="1" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="B166" s="2">
         <v>0.0</v>
@@ -6357,7 +6357,7 @@
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="1" t="s">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="B167" s="2">
         <v>0.0</v>
@@ -6365,7 +6365,7 @@
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="1" t="s">
-        <v>243</v>
+        <v>290</v>
       </c>
       <c r="B168" s="2">
         <v>0.0</v>
@@ -6373,7 +6373,7 @@
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="1" t="s">
-        <v>245</v>
+        <v>292</v>
       </c>
       <c r="B169" s="2">
         <v>0.0</v>
@@ -6381,7 +6381,7 @@
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="1" t="s">
-        <v>246</v>
+        <v>294</v>
       </c>
       <c r="B170" s="2">
         <v>0.0</v>
@@ -6389,7 +6389,7 @@
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="1" t="s">
-        <v>248</v>
+        <v>295</v>
       </c>
       <c r="B171" s="2">
         <v>0.0</v>
@@ -6397,7 +6397,7 @@
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="1" t="s">
-        <v>249</v>
+        <v>297</v>
       </c>
       <c r="B172" s="2">
         <v>0.0</v>
@@ -6405,7 +6405,7 @@
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="1" t="s">
-        <v>251</v>
+        <v>298</v>
       </c>
       <c r="B173" s="2">
         <v>0.0</v>
@@ -6413,7 +6413,7 @@
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="1" t="s">
-        <v>252</v>
+        <v>300</v>
       </c>
       <c r="B174" s="2">
         <v>0.0</v>
@@ -6421,7 +6421,7 @@
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="1" t="s">
-        <v>253</v>
+        <v>301</v>
       </c>
       <c r="B175" s="2">
         <v>0.0</v>
@@ -6429,7 +6429,7 @@
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="1" t="s">
-        <v>254</v>
+        <v>303</v>
       </c>
       <c r="B176" s="2">
         <v>0.0</v>
@@ -6437,7 +6437,7 @@
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="1" t="s">
-        <v>255</v>
+        <v>305</v>
       </c>
       <c r="B177" s="2">
         <v>0.0</v>
@@ -6445,7 +6445,7 @@
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="1" t="s">
-        <v>256</v>
+        <v>306</v>
       </c>
       <c r="B178" s="2">
         <v>0.0</v>
@@ -6453,7 +6453,7 @@
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="1" t="s">
-        <v>257</v>
+        <v>308</v>
       </c>
       <c r="B179" s="2">
         <v>0.0</v>
@@ -6461,7 +6461,7 @@
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="1" t="s">
-        <v>258</v>
+        <v>309</v>
       </c>
       <c r="B180" s="2">
         <v>0.0</v>
@@ -6469,7 +6469,7 @@
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="1" t="s">
-        <v>259</v>
+        <v>311</v>
       </c>
       <c r="B181" s="2">
         <v>0.0</v>
@@ -6477,7 +6477,7 @@
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="1" t="s">
-        <v>260</v>
+        <v>313</v>
       </c>
       <c r="B182" s="2">
         <v>0.0</v>
@@ -6485,7 +6485,7 @@
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="1" t="s">
-        <v>261</v>
+        <v>314</v>
       </c>
       <c r="B183" s="2">
         <v>0.0</v>
@@ -6493,7 +6493,7 @@
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="1" t="s">
-        <v>262</v>
+        <v>316</v>
       </c>
       <c r="B184" s="2">
         <v>0.0</v>
@@ -6501,7 +6501,7 @@
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="1" t="s">
-        <v>263</v>
+        <v>318</v>
       </c>
       <c r="B185" s="2">
         <v>0.0</v>
@@ -6509,7 +6509,7 @@
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="1" t="s">
-        <v>264</v>
+        <v>319</v>
       </c>
       <c r="B186" s="2">
         <v>0.0</v>
@@ -6517,7 +6517,7 @@
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="1" t="s">
-        <v>265</v>
+        <v>321</v>
       </c>
       <c r="B187" s="2">
         <v>0.0</v>
@@ -6525,7 +6525,7 @@
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="1" t="s">
-        <v>267</v>
+        <v>323</v>
       </c>
       <c r="B188" s="2">
         <v>0.0</v>
@@ -6533,7 +6533,7 @@
     </row>
     <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="1" t="s">
-        <v>268</v>
+        <v>325</v>
       </c>
       <c r="B189" s="2">
         <v>0.0</v>
@@ -6541,7 +6541,7 @@
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="1" t="s">
-        <v>270</v>
+        <v>327</v>
       </c>
       <c r="B190" s="2">
         <v>0.0</v>
@@ -6549,7 +6549,7 @@
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="1" t="s">
-        <v>271</v>
+        <v>329</v>
       </c>
       <c r="B191" s="2">
         <v>0.0</v>
@@ -6557,7 +6557,7 @@
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="1" t="s">
-        <v>272</v>
+        <v>331</v>
       </c>
       <c r="B192" s="2">
         <v>0.0</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="1" t="s">
-        <v>274</v>
+        <v>333</v>
       </c>
       <c r="B193" s="2">
         <v>0.0</v>
@@ -6573,7 +6573,7 @@
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="1" t="s">
-        <v>275</v>
+        <v>335</v>
       </c>
       <c r="B194" s="2">
         <v>0.0</v>
@@ -6581,7 +6581,7 @@
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="1" t="s">
-        <v>277</v>
+        <v>337</v>
       </c>
       <c r="B195" s="2">
         <v>0.0</v>
@@ -6589,7 +6589,7 @@
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="1" t="s">
-        <v>278</v>
+        <v>339</v>
       </c>
       <c r="B196" s="2">
         <v>0.0</v>
@@ -6597,7 +6597,7 @@
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="1" t="s">
-        <v>280</v>
+        <v>341</v>
       </c>
       <c r="B197" s="2">
         <v>0.0</v>
@@ -6605,7 +6605,7 @@
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="1" t="s">
-        <v>281</v>
+        <v>342</v>
       </c>
       <c r="B198" s="2">
         <v>0.0</v>
@@ -6613,7 +6613,7 @@
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="1" t="s">
-        <v>283</v>
+        <v>344</v>
       </c>
       <c r="B199" s="2">
         <v>0.0</v>
@@ -6621,7 +6621,7 @@
     </row>
     <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="1" t="s">
-        <v>284</v>
+        <v>345</v>
       </c>
       <c r="B200" s="2">
         <v>0.0</v>
@@ -6629,7 +6629,7 @@
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="1" t="s">
-        <v>285</v>
+        <v>347</v>
       </c>
       <c r="B201" s="2">
         <v>0.0</v>
@@ -6637,7 +6637,7 @@
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="1" t="s">
-        <v>286</v>
+        <v>349</v>
       </c>
       <c r="B202" s="2">
         <v>0.0</v>
@@ -6645,7 +6645,7 @@
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="1" t="s">
-        <v>287</v>
+        <v>350</v>
       </c>
       <c r="B203" s="2">
         <v>0.0</v>
@@ -6653,7 +6653,7 @@
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="1" t="s">
-        <v>288</v>
+        <v>352</v>
       </c>
       <c r="B204" s="2">
         <v>0.0</v>
@@ -6661,7 +6661,7 @@
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="1" t="s">
-        <v>289</v>
+        <v>354</v>
       </c>
       <c r="B205" s="2">
         <v>0.0</v>
@@ -6669,7 +6669,7 @@
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="1" t="s">
-        <v>291</v>
+        <v>355</v>
       </c>
       <c r="B206" s="2">
         <v>0.0</v>
@@ -6677,7 +6677,7 @@
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="1" t="s">
-        <v>292</v>
+        <v>357</v>
       </c>
       <c r="B207" s="2">
         <v>0.0</v>
@@ -6685,7 +6685,7 @@
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="1" t="s">
-        <v>294</v>
+        <v>358</v>
       </c>
       <c r="B208" s="2">
         <v>0.0</v>
@@ -6693,7 +6693,7 @@
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="1" t="s">
-        <v>295</v>
+        <v>360</v>
       </c>
       <c r="B209" s="2">
         <v>0.0</v>
@@ -6701,7 +6701,7 @@
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="1" t="s">
-        <v>297</v>
+        <v>362</v>
       </c>
       <c r="B210" s="2">
         <v>0.0</v>
@@ -6709,7 +6709,7 @@
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="1" t="s">
-        <v>298</v>
+        <v>363</v>
       </c>
       <c r="B211" s="2">
         <v>0.0</v>
@@ -6717,7 +6717,7 @@
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="1" t="s">
-        <v>300</v>
+        <v>365</v>
       </c>
       <c r="B212" s="2">
         <v>0.0</v>
@@ -6725,7 +6725,7 @@
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="1" t="s">
-        <v>301</v>
+        <v>367</v>
       </c>
       <c r="B213" s="2">
         <v>0.0</v>
@@ -6733,7 +6733,7 @@
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="1" t="s">
-        <v>303</v>
+        <v>369</v>
       </c>
       <c r="B214" s="2">
         <v>0.0</v>
@@ -6741,7 +6741,7 @@
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="1" t="s">
-        <v>304</v>
+        <v>370</v>
       </c>
       <c r="B215" s="2">
         <v>0.0</v>
@@ -6749,7 +6749,7 @@
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="1" t="s">
-        <v>306</v>
+        <v>372</v>
       </c>
       <c r="B216" s="2">
         <v>0.0</v>
@@ -6757,7 +6757,7 @@
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="1" t="s">
-        <v>307</v>
+        <v>374</v>
       </c>
       <c r="B217" s="2">
         <v>0.0</v>
@@ -6765,7 +6765,7 @@
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="1" t="s">
-        <v>309</v>
+        <v>375</v>
       </c>
       <c r="B218" s="2">
         <v>0.0</v>
@@ -6773,7 +6773,7 @@
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="1" t="s">
-        <v>310</v>
+        <v>377</v>
       </c>
       <c r="B219" s="2">
         <v>0.0</v>
@@ -6781,7 +6781,7 @@
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="1" t="s">
-        <v>312</v>
+        <v>378</v>
       </c>
       <c r="B220" s="2">
         <v>0.0</v>
@@ -6789,7 +6789,7 @@
     </row>
     <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="1" t="s">
-        <v>313</v>
+        <v>380</v>
       </c>
       <c r="B221" s="2">
         <v>0.0</v>
@@ -6797,7 +6797,7 @@
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="1" t="s">
-        <v>315</v>
+        <v>382</v>
       </c>
       <c r="B222" s="2">
         <v>0.0</v>
@@ -6805,7 +6805,7 @@
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="1" t="s">
-        <v>316</v>
+        <v>383</v>
       </c>
       <c r="B223" s="2">
         <v>0.0</v>
@@ -6813,7 +6813,7 @@
     </row>
     <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="1" t="s">
-        <v>317</v>
+        <v>385</v>
       </c>
       <c r="B224" s="2">
         <v>0.0</v>
@@ -6821,7 +6821,7 @@
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="1" t="s">
-        <v>319</v>
+        <v>386</v>
       </c>
       <c r="B225" s="2">
         <v>0.0</v>
@@ -6829,7 +6829,7 @@
     </row>
     <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="1" t="s">
-        <v>320</v>
+        <v>388</v>
       </c>
       <c r="B226" s="2">
         <v>0.0</v>
@@ -6837,7 +6837,7 @@
     </row>
     <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="1" t="s">
-        <v>322</v>
+        <v>390</v>
       </c>
       <c r="B227" s="2">
         <v>0.0</v>
@@ -6845,7 +6845,7 @@
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="1" t="s">
-        <v>323</v>
+        <v>391</v>
       </c>
       <c r="B228" s="2">
         <v>0.0</v>
@@ -6853,7 +6853,7 @@
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="1" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="B229" s="2">
         <v>0.0</v>
@@ -6861,7 +6861,7 @@
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="1" t="s">
-        <v>326</v>
+        <v>395</v>
       </c>
       <c r="B230" s="2">
         <v>0.0</v>
@@ -6869,7 +6869,7 @@
     </row>
     <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="1" t="s">
-        <v>328</v>
+        <v>396</v>
       </c>
       <c r="B231" s="2">
         <v>0.0</v>
@@ -6877,7 +6877,7 @@
     </row>
     <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="1" t="s">
-        <v>330</v>
+        <v>398</v>
       </c>
       <c r="B232" s="2">
         <v>0.0</v>
@@ -6885,7 +6885,7 @@
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="1" t="s">
-        <v>331</v>
+        <v>399</v>
       </c>
       <c r="B233" s="2">
         <v>0.0</v>
@@ -6893,7 +6893,7 @@
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="1" t="s">
-        <v>333</v>
+        <v>401</v>
       </c>
       <c r="B234" s="2">
         <v>0.0</v>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="1" t="s">
-        <v>335</v>
+        <v>402</v>
       </c>
       <c r="B235" s="2">
         <v>0.0</v>
@@ -6909,7 +6909,7 @@
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="1" t="s">
-        <v>337</v>
+        <v>404</v>
       </c>
       <c r="B236" s="2">
         <v>0.0</v>
@@ -6917,7 +6917,7 @@
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="1" t="s">
-        <v>338</v>
+        <v>405</v>
       </c>
       <c r="B237" s="2">
         <v>0.0</v>
@@ -6925,7 +6925,7 @@
     </row>
     <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="1" t="s">
-        <v>340</v>
+        <v>407</v>
       </c>
       <c r="B238" s="2">
         <v>0.0</v>
@@ -6933,7 +6933,7 @@
     </row>
     <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="1" t="s">
-        <v>341</v>
+        <v>408</v>
       </c>
       <c r="B239" s="2">
         <v>0.0</v>
@@ -6941,7 +6941,7 @@
     </row>
     <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="1" t="s">
-        <v>343</v>
+        <v>409</v>
       </c>
       <c r="B240" s="2">
         <v>0.0</v>
@@ -6949,7 +6949,7 @@
     </row>
     <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="1" t="s">
-        <v>344</v>
+        <v>410</v>
       </c>
       <c r="B241" s="2">
         <v>0.0</v>
@@ -6957,7 +6957,7 @@
     </row>
     <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="1" t="s">
-        <v>346</v>
+        <v>411</v>
       </c>
       <c r="B242" s="2">
         <v>0.0</v>
@@ -6965,7 +6965,7 @@
     </row>
     <row r="243" ht="15.75" customHeight="1">
       <c r="A243" s="1" t="s">
-        <v>347</v>
+        <v>412</v>
       </c>
       <c r="B243" s="2">
         <v>0.0</v>
@@ -6973,7 +6973,7 @@
     </row>
     <row r="244" ht="15.75" customHeight="1">
       <c r="A244" s="1" t="s">
-        <v>349</v>
+        <v>413</v>
       </c>
       <c r="B244" s="2">
         <v>0.0</v>
@@ -6981,7 +6981,7 @@
     </row>
     <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="1" t="s">
-        <v>350</v>
+        <v>414</v>
       </c>
       <c r="B245" s="2">
         <v>0.0</v>
@@ -6989,7 +6989,7 @@
     </row>
     <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="1" t="s">
-        <v>352</v>
+        <v>415</v>
       </c>
       <c r="B246" s="2">
         <v>0.0</v>
@@ -6997,7 +6997,7 @@
     </row>
     <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="1" t="s">
-        <v>353</v>
+        <v>416</v>
       </c>
       <c r="B247" s="2">
         <v>0.0</v>
@@ -7005,7 +7005,7 @@
     </row>
     <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="1" t="s">
-        <v>354</v>
+        <v>417</v>
       </c>
       <c r="B248" s="2">
         <v>0.0</v>
@@ -7013,7 +7013,7 @@
     </row>
     <row r="249" ht="15.75" customHeight="1">
       <c r="A249" s="1" t="s">
-        <v>355</v>
+        <v>418</v>
       </c>
       <c r="B249" s="2">
         <v>0.0</v>
@@ -7021,7 +7021,7 @@
     </row>
     <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="1" t="s">
-        <v>357</v>
+        <v>419</v>
       </c>
       <c r="B250" s="2">
         <v>0.0</v>
@@ -7029,7 +7029,7 @@
     </row>
     <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="1" t="s">
-        <v>359</v>
+        <v>420</v>
       </c>
       <c r="B251" s="2">
         <v>0.0</v>
@@ -7037,7 +7037,7 @@
     </row>
     <row r="252" ht="15.75" customHeight="1">
       <c r="A252" s="1" t="s">
-        <v>360</v>
+        <v>421</v>
       </c>
       <c r="B252" s="2">
         <v>0.0</v>
@@ -7045,7 +7045,7 @@
     </row>
     <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="1" t="s">
-        <v>362</v>
+        <v>422</v>
       </c>
       <c r="B253" s="2">
         <v>0.0</v>
@@ -7053,7 +7053,7 @@
     </row>
     <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="1" t="s">
-        <v>363</v>
+        <v>423</v>
       </c>
       <c r="B254" s="2">
         <v>0.0</v>
@@ -7061,7 +7061,7 @@
     </row>
     <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="1" t="s">
-        <v>365</v>
+        <v>424</v>
       </c>
       <c r="B255" s="2">
         <v>0.0</v>
@@ -7069,7 +7069,7 @@
     </row>
     <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="1" t="s">
-        <v>366</v>
+        <v>425</v>
       </c>
       <c r="B256" s="2">
         <v>0.0</v>
@@ -7077,7 +7077,7 @@
     </row>
     <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="1" t="s">
-        <v>368</v>
+        <v>426</v>
       </c>
       <c r="B257" s="2">
         <v>0.0</v>
@@ -7085,7 +7085,7 @@
     </row>
     <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="1" t="s">
-        <v>369</v>
+        <v>427</v>
       </c>
       <c r="B258" s="2">
         <v>0.0</v>
@@ -7093,7 +7093,7 @@
     </row>
     <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="1" t="s">
-        <v>370</v>
+        <v>428</v>
       </c>
       <c r="B259" s="2">
         <v>0.0</v>
@@ -7101,7 +7101,7 @@
     </row>
     <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="1" t="s">
-        <v>372</v>
+        <v>429</v>
       </c>
       <c r="B260" s="2">
         <v>0.0</v>
@@ -7109,7 +7109,7 @@
     </row>
     <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="1" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="B261" s="2">
         <v>0.0</v>
@@ -7117,7 +7117,7 @@
     </row>
     <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="1" t="s">
-        <v>375</v>
+        <v>431</v>
       </c>
       <c r="B262" s="2">
         <v>0.0</v>
@@ -7125,7 +7125,7 @@
     </row>
     <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="1" t="s">
-        <v>376</v>
+        <v>432</v>
       </c>
       <c r="B263" s="2">
         <v>0.0</v>
@@ -7133,7 +7133,7 @@
     </row>
     <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="1" t="s">
-        <v>378</v>
+        <v>433</v>
       </c>
       <c r="B264" s="2">
         <v>0.0</v>
@@ -7141,7 +7141,7 @@
     </row>
     <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="1" t="s">
-        <v>379</v>
+        <v>434</v>
       </c>
       <c r="B265" s="2">
         <v>0.0</v>
@@ -7149,7 +7149,7 @@
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="1" t="s">
-        <v>381</v>
+        <v>435</v>
       </c>
       <c r="B266" s="2">
         <v>0.0</v>
@@ -7157,7 +7157,7 @@
     </row>
     <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="1" t="s">
-        <v>382</v>
+        <v>436</v>
       </c>
       <c r="B267" s="2">
         <v>0.0</v>
@@ -7165,7 +7165,7 @@
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="1" t="s">
-        <v>384</v>
+        <v>437</v>
       </c>
       <c r="B268" s="2">
         <v>0.0</v>
@@ -7173,7 +7173,7 @@
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="1" t="s">
-        <v>386</v>
+        <v>438</v>
       </c>
       <c r="B269" s="2">
         <v>0.0</v>
@@ -7181,7 +7181,7 @@
     </row>
     <row r="270" ht="15.75" customHeight="1">
       <c r="A270" s="1" t="s">
-        <v>388</v>
+        <v>439</v>
       </c>
       <c r="B270" s="2">
         <v>0.0</v>
@@ -7189,7 +7189,7 @@
     </row>
     <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="1" t="s">
-        <v>389</v>
+        <v>440</v>
       </c>
       <c r="B271" s="2">
         <v>0.0</v>
@@ -7197,7 +7197,7 @@
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="1" t="s">
-        <v>391</v>
+        <v>441</v>
       </c>
       <c r="B272" s="2">
         <v>0.0</v>
@@ -7205,7 +7205,7 @@
     </row>
     <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="1" t="s">
-        <v>392</v>
+        <v>442</v>
       </c>
       <c r="B273" s="2">
         <v>0.0</v>
@@ -7213,7 +7213,7 @@
     </row>
     <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="1" t="s">
-        <v>394</v>
+        <v>443</v>
       </c>
       <c r="B274" s="2">
         <v>0.0</v>
@@ -7221,7 +7221,7 @@
     </row>
     <row r="275" ht="15.75" customHeight="1">
       <c r="A275" s="1" t="s">
-        <v>395</v>
+        <v>444</v>
       </c>
       <c r="B275" s="2">
         <v>0.0</v>
@@ -7229,7 +7229,7 @@
     </row>
     <row r="276" ht="15.75" customHeight="1">
       <c r="A276" s="1" t="s">
-        <v>397</v>
+        <v>445</v>
       </c>
       <c r="B276" s="2">
         <v>0.0</v>
@@ -7237,7 +7237,7 @@
     </row>
     <row r="277" ht="15.75" customHeight="1">
       <c r="A277" s="1" t="s">
-        <v>400</v>
+        <v>446</v>
       </c>
       <c r="B277" s="2">
         <v>0.0</v>
@@ -7245,7 +7245,7 @@
     </row>
     <row r="278" ht="15.75" customHeight="1">
       <c r="A278" s="1" t="s">
-        <v>401</v>
+        <v>447</v>
       </c>
       <c r="B278" s="2">
         <v>0.0</v>
@@ -7253,7 +7253,7 @@
     </row>
     <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="1" t="s">
-        <v>403</v>
+        <v>448</v>
       </c>
       <c r="B279" s="2">
         <v>0.0</v>
@@ -7261,7 +7261,7 @@
     </row>
     <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="1" t="s">
-        <v>404</v>
+        <v>449</v>
       </c>
       <c r="B280" s="2">
         <v>0.0</v>
@@ -7269,7 +7269,7 @@
     </row>
     <row r="281" ht="15.75" customHeight="1">
       <c r="A281" s="1" t="s">
-        <v>406</v>
+        <v>450</v>
       </c>
       <c r="B281" s="2">
         <v>0.0</v>
@@ -7277,7 +7277,7 @@
     </row>
     <row r="282" ht="15.75" customHeight="1">
       <c r="A282" s="1" t="s">
-        <v>407</v>
+        <v>451</v>
       </c>
       <c r="B282" s="2">
         <v>0.0</v>
@@ -7285,7 +7285,7 @@
     </row>
     <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="1" t="s">
-        <v>409</v>
+        <v>452</v>
       </c>
       <c r="B283" s="2">
         <v>0.0</v>
@@ -7293,7 +7293,7 @@
     </row>
     <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="1" t="s">
-        <v>410</v>
+        <v>453</v>
       </c>
       <c r="B284" s="2">
         <v>0.0</v>
@@ -7301,7 +7301,7 @@
     </row>
     <row r="285" ht="15.75" customHeight="1">
       <c r="A285" s="1" t="s">
-        <v>412</v>
+        <v>454</v>
       </c>
       <c r="B285" s="2">
         <v>0.0</v>
@@ -7309,7 +7309,7 @@
     </row>
     <row r="286" ht="15.75" customHeight="1">
       <c r="A286" s="1" t="s">
-        <v>413</v>
+        <v>455</v>
       </c>
       <c r="B286" s="2">
         <v>0.0</v>
@@ -7317,7 +7317,7 @@
     </row>
     <row r="287" ht="15.75" customHeight="1">
       <c r="A287" s="1" t="s">
-        <v>415</v>
+        <v>456</v>
       </c>
       <c r="B287" s="2">
         <v>0.0</v>
@@ -7325,7 +7325,7 @@
     </row>
     <row r="288" ht="15.75" customHeight="1">
       <c r="A288" s="1" t="s">
-        <v>416</v>
+        <v>457</v>
       </c>
       <c r="B288" s="2">
         <v>0.0</v>
@@ -7333,7 +7333,7 @@
     </row>
     <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="1" t="s">
-        <v>418</v>
+        <v>458</v>
       </c>
       <c r="B289" s="2">
         <v>0.0</v>
@@ -7341,7 +7341,7 @@
     </row>
     <row r="290" ht="15.75" customHeight="1">
       <c r="A290" s="1" t="s">
-        <v>419</v>
+        <v>459</v>
       </c>
       <c r="B290" s="2">
         <v>0.0</v>
@@ -7349,7 +7349,7 @@
     </row>
     <row r="291" ht="15.75" customHeight="1">
       <c r="A291" s="1" t="s">
-        <v>421</v>
+        <v>460</v>
       </c>
       <c r="B291" s="2">
         <v>0.0</v>
@@ -7357,7 +7357,7 @@
     </row>
     <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="1" t="s">
-        <v>422</v>
+        <v>461</v>
       </c>
       <c r="B292" s="2">
         <v>0.0</v>
@@ -7365,7 +7365,7 @@
     </row>
     <row r="293" ht="15.75" customHeight="1">
       <c r="A293" s="1" t="s">
-        <v>423</v>
+        <v>462</v>
       </c>
       <c r="B293" s="2">
         <v>0.0</v>
@@ -7373,7 +7373,7 @@
     </row>
     <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="1" t="s">
-        <v>424</v>
+        <v>463</v>
       </c>
       <c r="B294" s="2">
         <v>0.0</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="1" t="s">
-        <v>426</v>
+        <v>464</v>
       </c>
       <c r="B295" s="2">
         <v>0.0</v>
@@ -7389,7 +7389,7 @@
     </row>
     <row r="296" ht="15.75" customHeight="1">
       <c r="A296" s="1" t="s">
-        <v>428</v>
+        <v>465</v>
       </c>
       <c r="B296" s="2">
         <v>0.0</v>
@@ -7397,7 +7397,7 @@
     </row>
     <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="1" t="s">
-        <v>429</v>
+        <v>466</v>
       </c>
       <c r="B297" s="2">
         <v>0.0</v>
@@ -7405,7 +7405,7 @@
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="1" t="s">
-        <v>431</v>
+        <v>467</v>
       </c>
       <c r="B298" s="2">
         <v>0.0</v>
@@ -7413,7 +7413,7 @@
     </row>
     <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="1" t="s">
-        <v>432</v>
+        <v>468</v>
       </c>
       <c r="B299" s="2">
         <v>0.0</v>
@@ -7421,7 +7421,7 @@
     </row>
     <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="1" t="s">
-        <v>434</v>
+        <v>469</v>
       </c>
       <c r="B300" s="2">
         <v>0.0</v>
@@ -7429,7 +7429,7 @@
     </row>
     <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="1" t="s">
-        <v>435</v>
+        <v>470</v>
       </c>
       <c r="B301" s="2">
         <v>0.0</v>
@@ -7437,7 +7437,7 @@
     </row>
     <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="1" t="s">
-        <v>437</v>
+        <v>471</v>
       </c>
       <c r="B302" s="2">
         <v>0.0</v>
@@ -7445,7 +7445,7 @@
     </row>
     <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="1" t="s">
-        <v>438</v>
+        <v>472</v>
       </c>
       <c r="B303" s="2">
         <v>0.0</v>
@@ -7453,7 +7453,7 @@
     </row>
     <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="1" t="s">
-        <v>440</v>
+        <v>473</v>
       </c>
       <c r="B304" s="2">
         <v>0.0</v>
@@ -7461,7 +7461,7 @@
     </row>
     <row r="305" ht="15.75" customHeight="1">
       <c r="A305" s="1" t="s">
-        <v>442</v>
+        <v>474</v>
       </c>
       <c r="B305" s="2">
         <v>0.0</v>
@@ -7469,7 +7469,7 @@
     </row>
     <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="1" t="s">
-        <v>444</v>
+        <v>475</v>
       </c>
       <c r="B306" s="2">
         <v>0.0</v>
@@ -7477,7 +7477,7 @@
     </row>
     <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="1" t="s">
-        <v>445</v>
+        <v>476</v>
       </c>
       <c r="B307" s="2">
         <v>0.0</v>
@@ -7485,7 +7485,7 @@
     </row>
     <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="1" t="s">
-        <v>447</v>
+        <v>477</v>
       </c>
       <c r="B308" s="2">
         <v>0.0</v>
@@ -7493,7 +7493,7 @@
     </row>
     <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="1" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
       <c r="B309" s="2">
         <v>0.0</v>
@@ -7501,7 +7501,7 @@
     </row>
     <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="1" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
       <c r="B310" s="2">
         <v>0.0</v>
@@ -7509,7 +7509,7 @@
     </row>
     <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="1" t="s">
-        <v>452</v>
+        <v>480</v>
       </c>
       <c r="B311" s="2">
         <v>0.0</v>
@@ -7517,7 +7517,7 @@
     </row>
     <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="1" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="B312" s="2">
         <v>0.0</v>
@@ -7525,7 +7525,7 @@
     </row>
     <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="1" t="s">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="B313" s="2">
         <v>0.0</v>
@@ -7533,7 +7533,7 @@
     </row>
     <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="1" t="s">
-        <v>456</v>
+        <v>483</v>
       </c>
       <c r="B314" s="2">
         <v>0.0</v>
@@ -7541,7 +7541,7 @@
     </row>
     <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="1" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="B315" s="2">
         <v>0.0</v>
@@ -7549,7 +7549,7 @@
     </row>
     <row r="316" ht="15.75" customHeight="1">
       <c r="A316" s="1" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="B316" s="2">
         <v>0.0</v>
@@ -7557,7 +7557,7 @@
     </row>
     <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="1" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
       <c r="B317" s="2">
         <v>0.0</v>
@@ -7565,7 +7565,7 @@
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="1" t="s">
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="B318" s="2">
         <v>0.0</v>
@@ -7573,7 +7573,7 @@
     </row>
     <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="1" t="s">
-        <v>463</v>
+        <v>488</v>
       </c>
       <c r="B319" s="2">
         <v>0.0</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="1" t="s">
-        <v>464</v>
+        <v>489</v>
       </c>
       <c r="B320" s="2">
         <v>0.0</v>
@@ -7589,7 +7589,7 @@
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="1" t="s">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="B321" s="2">
         <v>0.0</v>
@@ -7597,7 +7597,7 @@
     </row>
     <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="1" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="B322" s="2">
         <v>0.0</v>
@@ -7605,7 +7605,7 @@
     </row>
     <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="1" t="s">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="B323" s="2">
         <v>0.0</v>
@@ -7613,7 +7613,7 @@
     </row>
     <row r="324" ht="15.75" customHeight="1">
       <c r="A324" s="1" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="B324" s="2">
         <v>0.0</v>
@@ -7621,7 +7621,7 @@
     </row>
     <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="1" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="B325" s="2">
         <v>0.0</v>
@@ -7629,7 +7629,7 @@
     </row>
     <row r="326" ht="15.75" customHeight="1">
       <c r="A326" s="1" t="s">
-        <v>473</v>
+        <v>495</v>
       </c>
       <c r="B326" s="2">
         <v>0.0</v>
@@ -7637,7 +7637,7 @@
     </row>
     <row r="327" ht="15.75" customHeight="1">
       <c r="A327" s="1" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
       <c r="B327" s="2">
         <v>0.0</v>
@@ -7645,7 +7645,7 @@
     </row>
     <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="1" t="s">
-        <v>476</v>
+        <v>497</v>
       </c>
       <c r="B328" s="2">
         <v>0.0</v>
@@ -7653,7 +7653,7 @@
     </row>
     <row r="329" ht="15.75" customHeight="1">
       <c r="A329" s="1" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="B329" s="2">
         <v>0.0</v>
@@ -7661,7 +7661,7 @@
     </row>
     <row r="330" ht="15.75" customHeight="1">
       <c r="A330" s="1" t="s">
-        <v>479</v>
+        <v>499</v>
       </c>
       <c r="B330" s="2">
         <v>0.0</v>
@@ -7669,7 +7669,7 @@
     </row>
     <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="1" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="B331" s="2">
         <v>0.0</v>
@@ -7677,7 +7677,7 @@
     </row>
     <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="1" t="s">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="B332" s="2">
         <v>0.0</v>
@@ -7685,7 +7685,7 @@
     </row>
     <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="1" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="B333" s="2">
         <v>0.0</v>
@@ -7693,7 +7693,7 @@
     </row>
     <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="1" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="B334" s="2">
         <v>0.0</v>
@@ -7701,7 +7701,7 @@
     </row>
     <row r="335" ht="15.75" customHeight="1">
       <c r="A335" s="1" t="s">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="B335" s="2">
         <v>0.0</v>
@@ -7709,7 +7709,7 @@
     </row>
     <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="1" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="B336" s="2">
         <v>0.0</v>
@@ -7717,7 +7717,7 @@
     </row>
     <row r="337" ht="15.75" customHeight="1">
       <c r="A337" s="1" t="s">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="B337" s="2">
         <v>0.0</v>
@@ -7725,7 +7725,7 @@
     </row>
     <row r="338" ht="15.75" customHeight="1">
       <c r="A338" s="1" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="B338" s="2">
         <v>0.0</v>
@@ -7733,7 +7733,7 @@
     </row>
     <row r="339" ht="15.75" customHeight="1">
       <c r="A339" s="1" t="s">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="B339" s="2">
         <v>0.0</v>
@@ -7741,7 +7741,7 @@
     </row>
     <row r="340" ht="15.75" customHeight="1">
       <c r="A340" s="1" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="B340" s="2">
         <v>0.0</v>
@@ -7749,7 +7749,7 @@
     </row>
     <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="1" t="s">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="B341" s="2">
         <v>0.0</v>
@@ -7757,7 +7757,7 @@
     </row>
     <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="1" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="B342" s="2">
         <v>0.0</v>
@@ -7765,7 +7765,7 @@
     </row>
     <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="1" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="B343" s="2">
         <v>0.0</v>
@@ -7773,7 +7773,7 @@
     </row>
     <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="1" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="B344" s="2">
         <v>0.0</v>
@@ -7781,7 +7781,7 @@
     </row>
     <row r="345" ht="15.75" customHeight="1">
       <c r="A345" s="1" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="B345" s="2">
         <v>0.0</v>
@@ -7789,7 +7789,7 @@
     </row>
     <row r="346" ht="15.75" customHeight="1">
       <c r="A346" s="1" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="B346" s="2">
         <v>0.0</v>
@@ -7797,7 +7797,7 @@
     </row>
     <row r="347" ht="15.75" customHeight="1">
       <c r="A347" s="1" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="B347" s="2">
         <v>0.0</v>
@@ -7805,7 +7805,7 @@
     </row>
     <row r="348" ht="15.75" customHeight="1">
       <c r="A348" s="1" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="B348" s="2">
         <v>0.0</v>
@@ -7813,7 +7813,7 @@
     </row>
     <row r="349" ht="15.75" customHeight="1">
       <c r="A349" s="1" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="B349" s="2">
         <v>0.0</v>
@@ -7821,7 +7821,7 @@
     </row>
     <row r="350" ht="15.75" customHeight="1">
       <c r="A350" s="1" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="B350" s="2">
         <v>0.0</v>
@@ -7829,7 +7829,7 @@
     </row>
     <row r="351" ht="15.75" customHeight="1">
       <c r="A351" s="1" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="B351" s="2">
         <v>0.0</v>
@@ -7837,7 +7837,7 @@
     </row>
     <row r="352" ht="15.75" customHeight="1">
       <c r="A352" s="1" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="B352" s="2">
         <v>0.0</v>
@@ -7845,7 +7845,7 @@
     </row>
     <row r="353" ht="15.75" customHeight="1">
       <c r="A353" s="1" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="B353" s="2">
         <v>0.0</v>
@@ -7853,7 +7853,7 @@
     </row>
     <row r="354" ht="15.75" customHeight="1">
       <c r="A354" s="1" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="B354" s="2">
         <v>0.0</v>
@@ -7861,7 +7861,7 @@
     </row>
     <row r="355" ht="15.75" customHeight="1">
       <c r="A355" s="1" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="B355" s="2">
         <v>0.0</v>
@@ -7869,7 +7869,7 @@
     </row>
     <row r="356" ht="15.75" customHeight="1">
       <c r="A356" s="1" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="B356" s="2">
         <v>0.0</v>
@@ -7877,7 +7877,7 @@
     </row>
     <row r="357" ht="15.75" customHeight="1">
       <c r="A357" s="1" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B357" s="2">
         <v>0.0</v>
@@ -7885,7 +7885,7 @@
     </row>
     <row r="358" ht="15.75" customHeight="1">
       <c r="A358" s="1" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="B358" s="2">
         <v>0.0</v>
@@ -7893,7 +7893,7 @@
     </row>
     <row r="359" ht="15.75" customHeight="1">
       <c r="A359" s="1" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B359" s="2">
         <v>0.0</v>
@@ -7901,7 +7901,7 @@
     </row>
     <row r="360" ht="15.75" customHeight="1">
       <c r="A360" s="1" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B360" s="2">
         <v>0.0</v>
@@ -7909,7 +7909,7 @@
     </row>
     <row r="361" ht="15.75" customHeight="1">
       <c r="A361" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B361" s="2">
         <v>0.0</v>
@@ -7917,7 +7917,7 @@
     </row>
     <row r="362" ht="15.75" customHeight="1">
       <c r="A362" s="1" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B362" s="2">
         <v>0.0</v>
@@ -7925,7 +7925,7 @@
     </row>
     <row r="363" ht="15.75" customHeight="1">
       <c r="A363" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B363" s="2">
         <v>0.0</v>
@@ -7933,7 +7933,7 @@
     </row>
     <row r="364" ht="15.75" customHeight="1">
       <c r="A364" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B364" s="2">
         <v>0.0</v>
@@ -7941,7 +7941,7 @@
     </row>
     <row r="365" ht="15.75" customHeight="1">
       <c r="A365" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B365" s="2">
         <v>0.0</v>
@@ -7949,7 +7949,7 @@
     </row>
     <row r="366" ht="15.75" customHeight="1">
       <c r="A366" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B366" s="2">
         <v>0.0</v>
@@ -7957,7 +7957,7 @@
     </row>
     <row r="367" ht="15.75" customHeight="1">
       <c r="A367" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B367" s="2">
         <v>0.0</v>
@@ -7965,7 +7965,7 @@
     </row>
     <row r="368" ht="15.75" customHeight="1">
       <c r="A368" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B368" s="2">
         <v>0.0</v>
@@ -10748,7 +10748,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="B2" s="1">
         <v>0.0</v>
@@ -10756,7 +10756,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1">
         <v>0.0</v>
@@ -10764,7 +10764,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="B4" s="1">
         <v>0.0</v>
@@ -10772,7 +10772,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1">
         <v>0.0</v>
